--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C98B833-E1F2-4D36-AEF0-9D3ADBDAC4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6922CA86-8F5E-4B44-A653-18D8A29B789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{A170A9F7-71A4-432C-8660-18A81FC209B7}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{BB7CBA46-C95D-4173-A505-56E1A4CACC11}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="122">
   <si>
     <t>Dados</t>
   </si>
@@ -103,6 +103,9 @@
     <t>25/02/2026</t>
   </si>
   <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
     <t>05/01/2026</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>26/02/2026</t>
   </si>
   <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
     <t>07/01/2026</t>
   </si>
   <si>
@@ -275,6 +281,9 @@
   </si>
   <si>
     <t>CI002027-CINDERELA_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - CINDER</t>
+  </si>
+  <si>
+    <t>CI002027-BELA_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - BELA 2</t>
   </si>
   <si>
     <t>CIPF002816-TOYSTORY_26-24 - CORPO GARRAFA FUN 600 ML - TOY&amp;STORY 202</t>
@@ -921,8 +930,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F50EBCA-FDEE-43BF-B388-F65DA9D638CA}">
-  <dimension ref="A1:O100"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A1E846-54CA-42EA-950F-0E85D7A7569C}">
+  <dimension ref="A1:O105"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -953,14 +962,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -974,40 +983,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1046,25 +1055,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1087,25 +1096,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1128,25 +1137,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1169,25 +1178,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1210,25 +1219,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1251,25 +1260,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1292,25 +1301,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1333,25 +1342,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1374,25 +1383,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1415,25 +1424,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1456,25 +1465,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1497,25 +1506,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1538,25 +1547,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1579,25 +1588,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1620,25 +1629,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1661,25 +1670,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1702,25 +1711,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1743,25 +1752,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1784,25 +1793,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1825,25 +1834,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1866,25 +1875,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1907,25 +1916,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1948,25 +1957,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1989,25 +1998,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2030,25 +2039,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2059,41 +2068,41 @@
     <row r="29" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D29" s="8">
-        <v>46027.4840625</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="E29" s="8">
-        <v>46027.4840625</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I29" s="7">
-        <v>1404289</v>
+        <v>1423124</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -2103,38 +2112,38 @@
         <v>6</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D30" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E30" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I30" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O30" s="7"/>
     </row>
@@ -2147,31 +2156,31 @@
         <v>17</v>
       </c>
       <c r="D31" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E31" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I31" s="7">
         <v>1394724</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2188,31 +2197,31 @@
         <v>17</v>
       </c>
       <c r="D32" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E32" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I32" s="7">
         <v>1394724</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2229,35 +2238,35 @@
         <v>17</v>
       </c>
       <c r="D33" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E33" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O33" s="7"/>
     </row>
@@ -2267,38 +2276,38 @@
         <v>6</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D34" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E34" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O34" s="7"/>
     </row>
@@ -2308,38 +2317,38 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D35" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E35" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O35" s="7"/>
     </row>
@@ -2349,34 +2358,34 @@
         <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E36" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2393,35 +2402,35 @@
         <v>29</v>
       </c>
       <c r="D37" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E37" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I37" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O37" s="7"/>
     </row>
@@ -2431,34 +2440,34 @@
         <v>6</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D38" s="8">
-        <v>46078.552407407406</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E38" s="8">
-        <v>46078.552407407406</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I38" s="7">
-        <v>1422286</v>
+        <v>1421099</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2472,38 +2481,38 @@
         <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D39" s="8">
-        <v>46080.522418981483</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="E39" s="8">
-        <v>46080.522418981483</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I39" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O39" s="7"/>
     </row>
@@ -2513,120 +2522,120 @@
         <v>6</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40" s="8">
-        <v>46080.532164351855</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="E40" s="8">
-        <v>46080.532164351855</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I40" s="7">
         <v>1422285</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O40" s="7"/>
     </row>
     <row r="41" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D41" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="E41" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I41" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O41" s="7"/>
     </row>
     <row r="42" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="E42" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I42" s="7">
-        <v>1405794</v>
+        <v>1422283</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O42" s="7"/>
     </row>
@@ -2636,38 +2645,38 @@
         <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D43" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E43" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O43" s="7"/>
     </row>
@@ -2677,38 +2686,38 @@
         <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E44" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I44" s="7">
         <v>1405794</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O44" s="7"/>
     </row>
@@ -2718,34 +2727,34 @@
         <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D45" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E45" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I45" s="7">
         <v>1405794</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2759,38 +2768,38 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D46" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E46" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I46" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O46" s="7"/>
     </row>
@@ -2800,38 +2809,38 @@
         <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D47" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E47" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I47" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O47" s="7"/>
     </row>
@@ -2841,38 +2850,38 @@
         <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D48" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E48" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I48" s="7">
-        <v>1410338</v>
+        <v>1411351</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>92</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O48" s="7"/>
     </row>
@@ -2882,38 +2891,38 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D49" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E49" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I49" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O49" s="7"/>
     </row>
@@ -2923,38 +2932,38 @@
         <v>7</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D50" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E50" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I50" s="7">
-        <v>1412987</v>
+        <v>1410338</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O50" s="7"/>
     </row>
@@ -2964,38 +2973,38 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D51" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E51" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I51" s="7">
-        <v>1421099</v>
+        <v>1412987</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -3005,34 +3014,34 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D52" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E52" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I52" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
@@ -3046,166 +3055,166 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E53" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I53" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
+        <v>2</v>
+      </c>
+      <c r="O53" s="7"/>
+    </row>
+    <row r="54" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A54" s="2"/>
+      <c r="B54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E54" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10">
         <v>3</v>
       </c>
-      <c r="O53" s="7"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A54" s="4"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="9">
+      <c r="O54" s="7"/>
+    </row>
+    <row r="55" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A55" s="2"/>
+      <c r="B55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E55" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I55" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10">
+        <v>3</v>
+      </c>
+      <c r="O55" s="7"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" s="4"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="9">
         <v>0</v>
       </c>
-      <c r="N54" s="9">
-        <v>227</v>
-      </c>
-      <c r="O54" s="9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
+      <c r="N56" s="9">
+        <v>231</v>
+      </c>
+      <c r="O56" s="9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B57" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
-      <c r="L55" s="12"/>
-      <c r="M55" s="12"/>
-      <c r="N55" s="12"/>
-      <c r="O55" s="12"/>
-    </row>
-    <row r="56" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A56" s="2"/>
-      <c r="B56" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D56" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="E56" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I56" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10">
-        <v>3</v>
-      </c>
-      <c r="O56" s="7"/>
-    </row>
-    <row r="57" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A57" s="2"/>
-      <c r="B57" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D57" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E57" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I57" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="L57" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10">
-        <v>1</v>
-      </c>
-      <c r="O57" s="7"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="12"/>
     </row>
     <row r="58" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
@@ -3213,38 +3222,38 @@
         <v>4</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D58" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E58" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I58" s="7">
-        <v>1406206</v>
+        <v>1386388</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O58" s="7"/>
     </row>
@@ -3254,38 +3263,38 @@
         <v>4</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D59" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E59" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I59" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>77</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O59" s="7"/>
     </row>
@@ -3295,38 +3304,38 @@
         <v>4</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D60" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E60" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I60" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O60" s="7"/>
     </row>
@@ -3339,35 +3348,35 @@
         <v>35</v>
       </c>
       <c r="D61" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E61" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I61" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O61" s="7"/>
     </row>
@@ -3377,38 +3386,38 @@
         <v>4</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D62" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E62" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I62" s="7">
         <v>1411990</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O62" s="7"/>
     </row>
@@ -3421,31 +3430,31 @@
         <v>36</v>
       </c>
       <c r="D63" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E63" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I63" s="7">
         <v>1411990</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
@@ -3462,199 +3471,199 @@
         <v>37</v>
       </c>
       <c r="D64" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E64" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I64" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O64" s="7"/>
     </row>
     <row r="65" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D65" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E65" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I65" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O65" s="7"/>
     </row>
     <row r="66" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D66" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E66" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I66" s="7">
-        <v>1394721</v>
+        <v>1410767</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O66" s="7"/>
     </row>
     <row r="67" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D67" s="8">
-        <v>46034.72855324074</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E67" s="8">
-        <v>46034.72855324074</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I67" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O67" s="7"/>
     </row>
     <row r="68" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D68" s="8">
-        <v>46037.838958333334</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E68" s="8">
-        <v>46037.838958333334</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I68" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3664,38 +3673,38 @@
         <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D69" s="8">
-        <v>46042.727754629632</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E69" s="8">
-        <v>46042.727754629632</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I69" s="7">
         <v>1394721</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3705,38 +3714,38 @@
         <v>5</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D70" s="8">
-        <v>46043.627881944441</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E70" s="8">
-        <v>46043.627881944441</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I70" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3746,38 +3755,38 @@
         <v>5</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D71" s="8">
-        <v>46052.626018518517</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E71" s="8">
-        <v>46052.626018518517</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I71" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L71" s="7" t="s">
         <v>110</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3787,38 +3796,38 @@
         <v>5</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D72" s="8">
-        <v>46053.632291666669</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E72" s="8">
-        <v>46053.632291666669</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I72" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L72" s="7" t="s">
         <v>110</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3831,31 +3840,31 @@
         <v>43</v>
       </c>
       <c r="D73" s="8">
-        <v>46071.601446759261</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E73" s="8">
-        <v>46071.601446759261</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I73" s="7">
-        <v>1418251</v>
+        <v>1394721</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
@@ -3869,34 +3878,34 @@
         <v>5</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D74" s="8">
-        <v>46076.679282407407</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E74" s="8">
-        <v>46076.679282407407</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I74" s="7">
-        <v>1422511</v>
+        <v>1410339</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
@@ -3910,38 +3919,38 @@
         <v>5</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D75" s="8">
-        <v>46077.591944444444</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E75" s="8">
-        <v>46077.591944444444</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I75" s="7">
-        <v>1422511</v>
+        <v>1411706</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3951,107 +3960,107 @@
         <v>5</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D76" s="8">
-        <v>46077.861296296294</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E76" s="8">
-        <v>46077.861296296294</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I76" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O76" s="7"/>
     </row>
     <row r="77" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D77" s="8">
-        <v>46027.633611111109</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E77" s="8">
-        <v>46027.633611111109</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I77" s="7">
-        <v>1404289</v>
+        <v>1418251</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K77" s="5" t="s">
         <v>105</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O77" s="7"/>
     </row>
     <row r="78" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D78" s="8">
-        <v>46029.802372685182</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E78" s="8">
-        <v>46029.802372685182</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I78" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>86</v>
@@ -4060,39 +4069,39 @@
         <v>105</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O78" s="7"/>
     </row>
     <row r="79" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D79" s="8">
-        <v>46030.908472222225</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E79" s="8">
-        <v>46030.908472222225</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>86</v>
@@ -4101,39 +4110,39 @@
         <v>105</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D80" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E80" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>86</v>
@@ -4142,11 +4151,11 @@
         <v>105</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O80" s="7"/>
     </row>
@@ -4156,38 +4165,38 @@
         <v>6</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D81" s="8">
-        <v>46076.8827662037</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E81" s="8">
-        <v>46076.8827662037</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I81" s="7">
-        <v>1422286</v>
+        <v>1404289</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>88</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O81" s="7"/>
     </row>
@@ -4197,38 +4206,38 @@
         <v>6</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D82" s="8">
-        <v>46078.867326388892</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E82" s="8">
-        <v>46078.867326388892</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I82" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4238,38 +4247,38 @@
         <v>6</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D83" s="8">
-        <v>46080.639293981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E83" s="8">
-        <v>46080.639293981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I83" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>89</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4279,38 +4288,38 @@
         <v>6</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D84" s="8">
-        <v>46080.716932870368</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E84" s="8">
-        <v>46080.716932870368</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I84" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>89</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4320,38 +4329,38 @@
         <v>6</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D85" s="8">
-        <v>46080.740543981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E85" s="8">
-        <v>46080.740543981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I85" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4361,243 +4370,243 @@
         <v>6</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D86" s="8">
-        <v>46081.588483796295</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E86" s="8">
-        <v>46081.588483796295</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I86" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O86" s="7"/>
     </row>
     <row r="87" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D87" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E87" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O87" s="7"/>
     </row>
     <row r="88" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D88" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E88" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I88" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O88" s="7"/>
     </row>
     <row r="89" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D89" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E89" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O89" s="7"/>
     </row>
     <row r="90" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D90" s="8">
-        <v>46028.866898148146</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E90" s="8">
-        <v>46028.866898148146</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" s="7">
-        <v>1402956</v>
+        <v>1422285</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O90" s="7"/>
     </row>
     <row r="91" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D91" s="8">
-        <v>46034.751261574071</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E91" s="8">
-        <v>46034.751261574071</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I91" s="7">
-        <v>1404958</v>
+        <v>1422283</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="O91" s="7"/>
     </row>
@@ -4607,38 +4616,38 @@
         <v>7</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D92" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E92" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I92" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O92" s="7"/>
     </row>
@@ -4648,38 +4657,38 @@
         <v>7</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D93" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E93" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I93" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O93" s="7"/>
     </row>
@@ -4689,38 +4698,38 @@
         <v>7</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D94" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E94" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I94" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O94" s="7"/>
     </row>
@@ -4730,38 +4739,38 @@
         <v>7</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D95" s="8">
-        <v>46069.700543981482</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E95" s="8">
-        <v>46069.700543981482</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I95" s="7">
-        <v>1411991</v>
+        <v>1402956</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4771,38 +4780,38 @@
         <v>7</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D96" s="8">
-        <v>46077.65824074074</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E96" s="8">
-        <v>46077.65824074074</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I96" s="7">
-        <v>1422285</v>
+        <v>1404958</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O96" s="7"/>
     </row>
@@ -4812,34 +4821,34 @@
         <v>7</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D97" s="8">
-        <v>46078.881018518521</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E97" s="8">
-        <v>46078.881018518521</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I97" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
@@ -4853,87 +4862,292 @@
         <v>7</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D98" s="8">
-        <v>46079.901782407411</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E98" s="8">
-        <v>46079.901782407411</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I98" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
+        <v>5</v>
+      </c>
+      <c r="O98" s="7"/>
+    </row>
+    <row r="99" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A99" s="2"/>
+      <c r="B99" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D99" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E99" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I99" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K99" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M99" s="10"/>
+      <c r="N99" s="10">
+        <v>3</v>
+      </c>
+      <c r="O99" s="7"/>
+    </row>
+    <row r="100" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A100" s="2"/>
+      <c r="B100" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E100" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I100" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K100" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M100" s="10"/>
+      <c r="N100" s="10">
+        <v>10</v>
+      </c>
+      <c r="O100" s="7"/>
+    </row>
+    <row r="101" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A101" s="2"/>
+      <c r="B101" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E101" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I101" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K101" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L101" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M101" s="10"/>
+      <c r="N101" s="10">
         <v>1</v>
       </c>
-      <c r="O98" s="7"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A99" s="4"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="9">
+      <c r="O101" s="7"/>
+    </row>
+    <row r="102" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A102" s="2"/>
+      <c r="B102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D102" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E102" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I102" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K102" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L102" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M102" s="10"/>
+      <c r="N102" s="10">
+        <v>1</v>
+      </c>
+      <c r="O102" s="7"/>
+    </row>
+    <row r="103" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A103" s="2"/>
+      <c r="B103" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E103" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I103" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K103" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M103" s="10"/>
+      <c r="N103" s="10">
+        <v>1</v>
+      </c>
+      <c r="O103" s="7"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A104" s="4"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="9">
         <v>0</v>
       </c>
-      <c r="N99" s="9">
-        <v>194</v>
-      </c>
-      <c r="O99" s="9">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A100" s="4"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="9">
-        <v>93</v>
-      </c>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="9">
+      <c r="N104" s="9">
+        <v>249</v>
+      </c>
+      <c r="O104" s="9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A105" s="4"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="9">
+        <v>98</v>
+      </c>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="9">
         <v>0</v>
       </c>
-      <c r="N100" s="9">
-        <v>421</v>
-      </c>
-      <c r="O100" s="9">
-        <v>93</v>
+      <c r="N105" s="9">
+        <v>480</v>
+      </c>
+      <c r="O105" s="9">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4943,8 +5157,9 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="B57:O57"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6922CA86-8F5E-4B44-A653-18D8A29B789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F858FCC-9CE8-4CA4-92C5-9A807034D2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{BB7CBA46-C95D-4173-A505-56E1A4CACC11}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{463ADD43-9B69-45E4-B575-83E842D7E9F2}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="124">
   <si>
     <t>Dados</t>
   </si>
@@ -106,6 +106,9 @@
     <t>02/03/2026</t>
   </si>
   <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
     <t>05/01/2026</t>
   </si>
   <si>
@@ -284,6 +287,9 @@
   </si>
   <si>
     <t>CI002027-BELA_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - BELA 2</t>
+  </si>
+  <si>
+    <t>CIPF002438-PRINCESAS-24 - GARRAFA ABRE FACIL530ML - IMPRESSAO DIGI</t>
   </si>
   <si>
     <t>CIPF002816-TOYSTORY_26-24 - CORPO GARRAFA FUN 600 ML - TOY&amp;STORY 202</t>
@@ -930,8 +936,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A1E846-54CA-42EA-950F-0E85D7A7569C}">
-  <dimension ref="A1:O105"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9BE098-F4B4-4F86-9F10-454FDC02BB27}">
+  <dimension ref="A1:O109"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -962,14 +968,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -983,40 +989,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1055,25 +1061,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1096,25 +1102,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1137,25 +1143,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1178,25 +1184,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1219,25 +1225,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1260,25 +1266,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1301,25 +1307,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1342,25 +1348,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1383,25 +1389,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1424,25 +1430,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1465,25 +1471,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1506,25 +1512,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1547,25 +1553,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1588,25 +1594,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1629,25 +1635,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1670,25 +1676,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1711,25 +1717,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1752,25 +1758,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1793,25 +1799,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1834,25 +1840,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1875,25 +1881,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1916,25 +1922,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1957,25 +1963,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1998,25 +2004,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2039,25 +2045,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2080,25 +2086,25 @@
         <v>46083.272581018522</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I29" s="7">
         <v>1423124</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2109,82 +2115,82 @@
     <row r="30" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="8">
-        <v>46027.4840625</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="E30" s="8">
-        <v>46027.4840625</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I30" s="7">
-        <v>1404289</v>
+        <v>1428373</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D31" s="8">
-        <v>46030.397997685184</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="E31" s="8">
-        <v>46030.397997685184</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I31" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>89</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O31" s="7"/>
     </row>
@@ -2194,38 +2200,38 @@
         <v>6</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D32" s="8">
-        <v>46030.408148148148</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E32" s="8">
-        <v>46030.408148148148</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I32" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O32" s="7"/>
     </row>
@@ -2238,31 +2244,31 @@
         <v>17</v>
       </c>
       <c r="D33" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E33" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2279,35 +2285,35 @@
         <v>17</v>
       </c>
       <c r="D34" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E34" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O34" s="7"/>
     </row>
@@ -2317,38 +2323,38 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D35" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E35" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O35" s="7"/>
     </row>
@@ -2358,38 +2364,38 @@
         <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D36" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E36" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O36" s="7"/>
     </row>
@@ -2399,38 +2405,38 @@
         <v>6</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D37" s="8">
-        <v>46043.565196759257</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E37" s="8">
-        <v>46043.565196759257</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I37" s="7">
         <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O37" s="7"/>
     </row>
@@ -2443,35 +2449,35 @@
         <v>30</v>
       </c>
       <c r="D38" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E38" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I38" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O38" s="7"/>
     </row>
@@ -2481,38 +2487,38 @@
         <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D39" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E39" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I39" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O39" s="7"/>
     </row>
@@ -2525,35 +2531,35 @@
         <v>31</v>
       </c>
       <c r="D40" s="8">
-        <v>46080.522418981483</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E40" s="8">
-        <v>46080.522418981483</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I40" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>92</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -2563,38 +2569,38 @@
         <v>6</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D41" s="8">
-        <v>46080.532164351855</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="E41" s="8">
-        <v>46080.532164351855</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I41" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O41" s="7"/>
     </row>
@@ -2604,157 +2610,157 @@
         <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D42" s="8">
-        <v>46083.531342592592</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="E42" s="8">
-        <v>46083.531342592592</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I42" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O42" s="7"/>
     </row>
     <row r="43" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D43" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="E43" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I43" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O43" s="7"/>
     </row>
     <row r="44" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D44" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="E44" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I44" s="7">
-        <v>1405794</v>
+        <v>1422283</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O44" s="7"/>
     </row>
     <row r="45" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" s="8">
-        <v>46043.385289351849</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="E45" s="8">
-        <v>46043.385289351849</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I45" s="7">
-        <v>1405794</v>
+        <v>1422283</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2768,34 +2774,34 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D46" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E46" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I46" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2809,38 +2815,38 @@
         <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D47" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E47" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I47" s="7">
         <v>1405794</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O47" s="7"/>
     </row>
@@ -2850,38 +2856,38 @@
         <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D48" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E48" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I48" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O48" s="7"/>
     </row>
@@ -2891,38 +2897,38 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D49" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E49" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I49" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O49" s="7"/>
     </row>
@@ -2935,35 +2941,35 @@
         <v>33</v>
       </c>
       <c r="D50" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E50" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I50" s="7">
-        <v>1410338</v>
+        <v>1405794</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O50" s="7"/>
     </row>
@@ -2973,38 +2979,38 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D51" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E51" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I51" s="7">
-        <v>1412987</v>
+        <v>1411351</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -3014,38 +3020,38 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D52" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E52" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I52" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -3055,38 +3061,38 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D53" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E53" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I53" s="7">
-        <v>1421099</v>
+        <v>1410338</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O53" s="7"/>
     </row>
@@ -3096,38 +3102,38 @@
         <v>7</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D54" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E54" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I54" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O54" s="7"/>
     </row>
@@ -3137,34 +3143,34 @@
         <v>7</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D55" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E55" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I55" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
@@ -3172,84 +3178,122 @@
       </c>
       <c r="O55" s="7"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A56" s="4"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="9">
-        <v>0</v>
-      </c>
-      <c r="N56" s="9">
-        <v>231</v>
-      </c>
-      <c r="O56" s="9">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
+    <row r="56" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A56" s="2"/>
+      <c r="B56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" s="8">
+        <v>46073.402627314812</v>
+      </c>
+      <c r="E56" s="8">
+        <v>46073.402627314812</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I56" s="7">
+        <v>1421099</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10">
         <v>2</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
+      <c r="O56" s="7"/>
+    </row>
+    <row r="57" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A57" s="2"/>
+      <c r="B57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E57" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10">
+        <v>3</v>
+      </c>
+      <c r="O57" s="7"/>
     </row>
     <row r="58" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D58" s="8">
-        <v>46027.666331018518</v>
+        <v>46077.554594907408</v>
       </c>
       <c r="E58" s="8">
-        <v>46027.666331018518</v>
+        <v>46077.554594907408</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>71</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I58" s="7">
-        <v>1386388</v>
+        <v>1422285</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
@@ -3260,125 +3304,87 @@
     <row r="59" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="8">
-        <v>46027.694131944445</v>
+        <v>46085.366041666668</v>
       </c>
       <c r="E59" s="8">
-        <v>46027.694131944445</v>
+        <v>46085.366041666668</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>71</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I59" s="7">
-        <v>1386388</v>
+        <v>1423125</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O59" s="7"/>
     </row>
-    <row r="60" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A60" s="2"/>
-      <c r="B60" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="E60" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I60" s="7">
-        <v>1406206</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10">
-        <v>11</v>
-      </c>
-      <c r="O60" s="7"/>
-    </row>
-    <row r="61" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A61" s="2"/>
-      <c r="B61" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="8">
-        <v>46059.905682870369</v>
-      </c>
-      <c r="E61" s="8">
-        <v>46059.905682870369</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I61" s="7">
-        <v>1411984</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10">
-        <v>9</v>
-      </c>
-      <c r="O61" s="7"/>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" s="4"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="9">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9">
+        <v>242</v>
+      </c>
+      <c r="O60" s="9">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
     </row>
     <row r="62" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
@@ -3386,38 +3392,38 @@
         <v>4</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D62" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E62" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I62" s="7">
-        <v>1411990</v>
+        <v>1386388</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>78</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O62" s="7"/>
     </row>
@@ -3427,38 +3433,38 @@
         <v>4</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D63" s="8">
-        <v>46065.655185185184</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E63" s="8">
-        <v>46065.655185185184</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I63" s="7">
-        <v>1411990</v>
+        <v>1386388</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>78</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O63" s="7"/>
     </row>
@@ -3468,38 +3474,38 @@
         <v>4</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D64" s="8">
-        <v>46066.613657407404</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E64" s="8">
-        <v>46066.613657407404</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I64" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O64" s="7"/>
     </row>
@@ -3509,38 +3515,38 @@
         <v>4</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D65" s="8">
-        <v>46066.670127314814</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E65" s="8">
-        <v>46066.670127314814</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I65" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O65" s="7"/>
     </row>
@@ -3550,38 +3556,38 @@
         <v>4</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D66" s="8">
-        <v>46079.703912037039</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E66" s="8">
-        <v>46079.703912037039</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I66" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -3591,38 +3597,38 @@
         <v>4</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D67" s="8">
-        <v>46084.877986111111</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E67" s="8">
-        <v>46084.877986111111</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I67" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="K67" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3632,34 +3638,34 @@
         <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D68" s="8">
-        <v>46084.883263888885</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E68" s="8">
-        <v>46084.883263888885</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I68" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="K68" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
@@ -3670,164 +3676,164 @@
     <row r="69" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D69" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E69" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I69" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K69" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O69" s="7"/>
     </row>
     <row r="70" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D70" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E70" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I70" s="7">
-        <v>1394721</v>
+        <v>1410767</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K70" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O70" s="7"/>
     </row>
     <row r="71" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D71" s="8">
-        <v>46034.72855324074</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E71" s="8">
-        <v>46034.72855324074</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I71" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O71" s="7"/>
     </row>
     <row r="72" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D72" s="8">
-        <v>46037.838958333334</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E72" s="8">
-        <v>46037.838958333334</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I72" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3837,38 +3843,38 @@
         <v>5</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D73" s="8">
-        <v>46042.727754629632</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E73" s="8">
-        <v>46042.727754629632</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I73" s="7">
         <v>1394721</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3878,38 +3884,38 @@
         <v>5</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D74" s="8">
-        <v>46043.627881944441</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E74" s="8">
-        <v>46043.627881944441</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I74" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3919,38 +3925,38 @@
         <v>5</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D75" s="8">
-        <v>46052.626018518517</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E75" s="8">
-        <v>46052.626018518517</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I75" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3960,38 +3966,38 @@
         <v>5</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D76" s="8">
-        <v>46053.632291666669</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E76" s="8">
-        <v>46053.632291666669</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I76" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -4001,34 +4007,34 @@
         <v>5</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D77" s="8">
-        <v>46071.601446759261</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E77" s="8">
-        <v>46071.601446759261</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I77" s="7">
-        <v>1418251</v>
+        <v>1394721</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
@@ -4042,34 +4048,34 @@
         <v>5</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D78" s="8">
-        <v>46076.679282407407</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E78" s="8">
-        <v>46076.679282407407</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I78" s="7">
-        <v>1422511</v>
+        <v>1410339</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
@@ -4083,38 +4089,38 @@
         <v>5</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D79" s="8">
-        <v>46077.591944444444</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E79" s="8">
-        <v>46077.591944444444</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I79" s="7">
-        <v>1422511</v>
+        <v>1411706</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4124,202 +4130,202 @@
         <v>5</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D80" s="8">
-        <v>46077.861296296294</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E80" s="8">
-        <v>46077.861296296294</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I80" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O80" s="7"/>
     </row>
     <row r="81" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D81" s="8">
-        <v>46027.633611111109</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E81" s="8">
-        <v>46027.633611111109</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I81" s="7">
-        <v>1404289</v>
+        <v>1418251</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O81" s="7"/>
     </row>
     <row r="82" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D82" s="8">
-        <v>46029.802372685182</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E82" s="8">
-        <v>46029.802372685182</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I82" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O82" s="7"/>
     </row>
     <row r="83" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D83" s="8">
-        <v>46030.908472222225</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E83" s="8">
-        <v>46030.908472222225</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I83" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O83" s="7"/>
     </row>
     <row r="84" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D84" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E84" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I84" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4329,38 +4335,38 @@
         <v>6</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D85" s="8">
-        <v>46076.8827662037</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E85" s="8">
-        <v>46076.8827662037</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I85" s="7">
-        <v>1422286</v>
+        <v>1404289</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4370,38 +4376,38 @@
         <v>6</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D86" s="8">
-        <v>46078.867326388892</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E86" s="8">
-        <v>46078.867326388892</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I86" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O86" s="7"/>
     </row>
@@ -4411,38 +4417,38 @@
         <v>6</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D87" s="8">
-        <v>46080.639293981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E87" s="8">
-        <v>46080.639293981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I87" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O87" s="7"/>
     </row>
@@ -4452,38 +4458,38 @@
         <v>6</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D88" s="8">
-        <v>46080.716932870368</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E88" s="8">
-        <v>46080.716932870368</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>66</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I88" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O88" s="7"/>
     </row>
@@ -4493,38 +4499,38 @@
         <v>6</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D89" s="8">
-        <v>46080.740543981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E89" s="8">
-        <v>46080.740543981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I89" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O89" s="7"/>
     </row>
@@ -4534,38 +4540,38 @@
         <v>6</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D90" s="8">
-        <v>46081.588483796295</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E90" s="8">
-        <v>46081.588483796295</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I90" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O90" s="7"/>
     </row>
@@ -4575,202 +4581,202 @@
         <v>6</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D91" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E91" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I91" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="O91" s="7"/>
     </row>
     <row r="92" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D92" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E92" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I92" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O92" s="7"/>
     </row>
     <row r="93" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D93" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E93" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I93" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O93" s="7"/>
     </row>
     <row r="94" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>48</v>
       </c>
       <c r="D94" s="8">
-        <v>46024.900324074071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E94" s="8">
-        <v>46024.900324074071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I94" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O94" s="7"/>
     </row>
     <row r="95" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D95" s="8">
-        <v>46028.866898148146</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E95" s="8">
-        <v>46028.866898148146</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I95" s="7">
-        <v>1402956</v>
+        <v>1422283</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L95" s="7" t="s">
         <v>113</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4780,38 +4786,38 @@
         <v>7</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D96" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E96" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I96" s="7">
-        <v>1404958</v>
+        <v>1398335</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O96" s="7"/>
     </row>
@@ -4821,38 +4827,38 @@
         <v>7</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="D97" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E97" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I97" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O97" s="7"/>
     </row>
@@ -4865,31 +4871,31 @@
         <v>49</v>
       </c>
       <c r="D98" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E98" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I98" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
@@ -4903,38 +4909,38 @@
         <v>7</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D99" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E99" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I99" s="7">
-        <v>1411991</v>
+        <v>1402956</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O99" s="7"/>
     </row>
@@ -4944,38 +4950,38 @@
         <v>7</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D100" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E100" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I100" s="7">
-        <v>1411991</v>
+        <v>1404958</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O100" s="7"/>
     </row>
@@ -4985,34 +4991,34 @@
         <v>7</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D101" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E101" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I101" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
@@ -5026,38 +5032,38 @@
         <v>7</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D102" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E102" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I102" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O102" s="7"/>
     </row>
@@ -5067,87 +5073,251 @@
         <v>7</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D103" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="E103" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I103" s="7">
-        <v>1423123</v>
+        <v>1411991</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10">
+        <v>3</v>
+      </c>
+      <c r="O103" s="7"/>
+    </row>
+    <row r="104" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A104" s="2"/>
+      <c r="B104" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D104" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E104" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K104" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L104" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M104" s="10"/>
+      <c r="N104" s="10">
+        <v>10</v>
+      </c>
+      <c r="O104" s="7"/>
+    </row>
+    <row r="105" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A105" s="2"/>
+      <c r="B105" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E105" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I105" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K105" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M105" s="10"/>
+      <c r="N105" s="10">
         <v>1</v>
       </c>
-      <c r="O103" s="7"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A104" s="4"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="9">
+      <c r="O105" s="7"/>
+    </row>
+    <row r="106" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A106" s="2"/>
+      <c r="B106" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D106" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E106" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I106" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K106" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L106" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10">
+        <v>1</v>
+      </c>
+      <c r="O106" s="7"/>
+    </row>
+    <row r="107" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A107" s="2"/>
+      <c r="B107" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D107" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E107" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I107" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K107" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M107" s="10"/>
+      <c r="N107" s="10">
+        <v>1</v>
+      </c>
+      <c r="O107" s="7"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="9">
         <v>0</v>
       </c>
-      <c r="N104" s="9">
+      <c r="N108" s="9">
         <v>249</v>
       </c>
-      <c r="O104" s="9">
+      <c r="O108" s="9">
         <v>46</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A105" s="4"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="9">
-        <v>98</v>
-      </c>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
-      <c r="M105" s="9">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="9">
+        <v>102</v>
+      </c>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="9">
         <v>0</v>
       </c>
-      <c r="N105" s="9">
-        <v>480</v>
-      </c>
-      <c r="O105" s="9">
-        <v>98</v>
+      <c r="N109" s="9">
+        <v>491</v>
+      </c>
+      <c r="O109" s="9">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -5157,9 +5327,8 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B57:O57"/>
+    <mergeCell ref="B61:O61"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0903554-4587-48B6-9CDA-69D4BBD6EFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82CF9C91-22AF-482B-90BE-611DD5789D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDC75864-2D3A-426D-8A84-ED2527537ED9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC936890-B410-417B-B4F6-9A40F5669DC1}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="128">
   <si>
     <t>Dados</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Turno : 2</t>
   </si>
   <si>
+    <t>29-CX-360G</t>
+  </si>
+  <si>
     <t>Data</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>27/02/2026</t>
   </si>
   <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
     <t>22/01/2026</t>
   </si>
   <si>
@@ -146,6 +152,9 @@
   </si>
   <si>
     <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>07/03/2026</t>
   </si>
   <si>
     <t>07/01/2026</t>
@@ -939,8 +948,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874E1856-81A4-4324-B49F-EF2BFD955075}">
-  <dimension ref="A1:O113"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B3390D-5B1E-447F-A8A7-8114E061DE83}">
+  <dimension ref="A1:O122"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -971,14 +980,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -989,43 +998,43 @@
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1055,7 +1064,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="8">
         <v>46046.443344907406</v>
@@ -1064,25 +1073,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1096,7 +1105,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="8">
         <v>46046.553217592591</v>
@@ -1105,25 +1114,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1137,7 +1146,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="8">
         <v>46050.493333333332</v>
@@ -1146,25 +1155,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1178,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="8">
         <v>46051.555428240739</v>
@@ -1187,25 +1196,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1219,7 +1228,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="8">
         <v>46053.377129629633</v>
@@ -1228,25 +1237,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1260,7 +1269,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="8">
         <v>46062.302418981482</v>
@@ -1269,25 +1278,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1301,7 +1310,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="8">
         <v>46062.570879629631</v>
@@ -1310,25 +1319,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1342,7 +1351,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="8">
         <v>46064.297777777778</v>
@@ -1351,25 +1360,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1383,7 +1392,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="8">
         <v>46064.455104166664</v>
@@ -1392,25 +1401,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1424,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="8">
         <v>46086.442870370367</v>
@@ -1433,25 +1442,25 @@
         <v>46086.442870370367</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I13" s="7">
         <v>1428327</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1465,7 +1474,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="8">
         <v>46028.331469907411</v>
@@ -1474,25 +1483,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I14" s="7">
         <v>1402958</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1506,7 +1515,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="8">
         <v>46030.306192129632</v>
@@ -1515,25 +1524,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1547,7 +1556,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="8">
         <v>46031.443101851852</v>
@@ -1556,25 +1565,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1588,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="8">
         <v>46035.530381944445</v>
@@ -1597,25 +1606,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I17" s="7">
         <v>1394721</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1629,7 +1638,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="8">
         <v>46046.391701388886</v>
@@ -1638,25 +1647,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1670,7 +1679,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="8">
         <v>46046.516597222224</v>
@@ -1679,25 +1688,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1711,7 +1720,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="8">
         <v>46048.278912037036</v>
@@ -1720,25 +1729,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1752,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="8">
         <v>46051.403391203705</v>
@@ -1761,25 +1770,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I21" s="7">
         <v>1410340</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1793,7 +1802,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="8">
         <v>46053.550381944442</v>
@@ -1802,25 +1811,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I22" s="7">
         <v>1411706</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1834,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="8">
         <v>46057.413171296299</v>
@@ -1843,25 +1852,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1875,7 +1884,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" s="8">
         <v>46058.357476851852</v>
@@ -1884,25 +1893,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1916,7 +1925,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" s="8">
         <v>46058.531793981485</v>
@@ -1925,25 +1934,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I25" s="7">
         <v>1411704</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1957,7 +1966,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="8">
         <v>46067.433020833334</v>
@@ -1966,25 +1975,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I26" s="7">
         <v>1418256</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1998,7 +2007,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" s="8">
         <v>46073.579664351855</v>
@@ -2007,25 +2016,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2039,7 +2048,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28" s="8">
         <v>46077.38318287037</v>
@@ -2048,25 +2057,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2080,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29" s="8">
         <v>46078.372766203705</v>
@@ -2089,25 +2098,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I29" s="7">
         <v>1422511</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2121,7 +2130,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" s="8">
         <v>46083.272581018522</v>
@@ -2130,25 +2139,25 @@
         <v>46083.272581018522</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I30" s="7">
         <v>1423124</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2162,7 +2171,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D31" s="8">
         <v>46085.323807870373</v>
@@ -2171,25 +2180,25 @@
         <v>46085.323807870373</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I31" s="7">
         <v>1428373</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2203,7 +2212,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D32" s="8">
         <v>46085.344675925924</v>
@@ -2212,25 +2221,25 @@
         <v>46085.344675925924</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I32" s="7">
         <v>1428373</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2244,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D33" s="8">
         <v>46086.434641203705</v>
@@ -2253,25 +2262,25 @@
         <v>46086.434641203705</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I33" s="7">
         <v>1428373</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2285,7 +2294,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D34" s="8">
         <v>46027.4840625</v>
@@ -2294,25 +2303,25 @@
         <v>46027.4840625</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I34" s="7">
         <v>1404289</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2326,7 +2335,7 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35" s="8">
         <v>46030.397997685184</v>
@@ -2335,25 +2344,25 @@
         <v>46030.397997685184</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2367,7 +2376,7 @@
         <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36" s="8">
         <v>46030.408148148148</v>
@@ -2376,25 +2385,25 @@
         <v>46030.408148148148</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2408,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D37" s="8">
         <v>46030.478854166664</v>
@@ -2417,25 +2426,25 @@
         <v>46030.478854166664</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I37" s="7">
         <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2449,7 +2458,7 @@
         <v>6</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D38" s="8">
         <v>46030.561284722222</v>
@@ -2458,25 +2467,25 @@
         <v>46030.561284722222</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I38" s="7">
         <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2490,7 +2499,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39" s="8">
         <v>46035.478368055556</v>
@@ -2499,25 +2508,25 @@
         <v>46035.478368055556</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I39" s="7">
         <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
@@ -2531,7 +2540,7 @@
         <v>6</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D40" s="8">
         <v>46043.385474537034</v>
@@ -2540,25 +2549,25 @@
         <v>46043.385474537034</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I40" s="7">
         <v>1394724</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
@@ -2572,7 +2581,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D41" s="8">
         <v>46043.565196759257</v>
@@ -2581,25 +2590,25 @@
         <v>46043.565196759257</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I41" s="7">
         <v>1394724</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
@@ -2613,7 +2622,7 @@
         <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D42" s="8">
         <v>46069.559953703705</v>
@@ -2622,25 +2631,25 @@
         <v>46069.559953703705</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I42" s="7">
         <v>1421099</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
@@ -2654,7 +2663,7 @@
         <v>6</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43" s="8">
         <v>46078.552407407406</v>
@@ -2663,25 +2672,25 @@
         <v>46078.552407407406</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I43" s="7">
         <v>1422286</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
@@ -2695,7 +2704,7 @@
         <v>6</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44" s="8">
         <v>46080.522418981483</v>
@@ -2704,25 +2713,25 @@
         <v>46080.522418981483</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I44" s="7">
         <v>1422285</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
@@ -2736,7 +2745,7 @@
         <v>6</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D45" s="8">
         <v>46080.532164351855</v>
@@ -2745,25 +2754,25 @@
         <v>46080.532164351855</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I45" s="7">
         <v>1422285</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2777,7 +2786,7 @@
         <v>6</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" s="8">
         <v>46083.531342592592</v>
@@ -2786,25 +2795,25 @@
         <v>46083.531342592592</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I46" s="7">
         <v>1422283</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2818,7 +2827,7 @@
         <v>6</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D47" s="8">
         <v>46085.365902777776</v>
@@ -2827,25 +2836,25 @@
         <v>46085.365902777776</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I47" s="7">
         <v>1422283</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
@@ -2859,7 +2868,7 @@
         <v>6</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D48" s="8">
         <v>46086.317847222221</v>
@@ -2868,25 +2877,25 @@
         <v>46086.317847222221</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I48" s="7">
         <v>1428242</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
@@ -2897,78 +2906,78 @@
     <row r="49" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D49" s="8">
-        <v>46035.47824074074</v>
+        <v>46087.292048611111</v>
       </c>
       <c r="E49" s="8">
-        <v>46035.47824074074</v>
+        <v>46087.292048611111</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I49" s="7">
-        <v>1404958</v>
+        <v>1422282</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O49" s="7"/>
     </row>
     <row r="50" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D50" s="8">
-        <v>46043.385196759256</v>
+        <v>46087.575972222221</v>
       </c>
       <c r="E50" s="8">
-        <v>46043.385196759256</v>
+        <v>46087.575972222221</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I50" s="7">
-        <v>1405794</v>
+        <v>1422282</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -2982,38 +2991,38 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D51" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E51" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I51" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -3023,38 +3032,38 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D52" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E52" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I52" s="7">
         <v>1405794</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -3064,34 +3073,34 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D53" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E53" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I53" s="7">
         <v>1405794</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
@@ -3105,38 +3114,38 @@
         <v>7</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D54" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E54" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I54" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O54" s="7"/>
     </row>
@@ -3146,38 +3155,38 @@
         <v>7</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D55" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E55" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I55" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O55" s="7"/>
     </row>
@@ -3187,38 +3196,38 @@
         <v>7</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D56" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E56" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I56" s="7">
-        <v>1410338</v>
+        <v>1411351</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>99</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O56" s="7"/>
     </row>
@@ -3228,38 +3237,38 @@
         <v>7</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E57" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I57" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O57" s="7"/>
     </row>
@@ -3269,38 +3278,38 @@
         <v>7</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D58" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E58" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I58" s="7">
-        <v>1412987</v>
+        <v>1410338</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O58" s="7"/>
     </row>
@@ -3310,38 +3319,38 @@
         <v>7</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D59" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E59" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I59" s="7">
-        <v>1421099</v>
+        <v>1412987</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O59" s="7"/>
     </row>
@@ -3351,34 +3360,34 @@
         <v>7</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D60" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E60" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I60" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
@@ -3395,35 +3404,35 @@
         <v>26</v>
       </c>
       <c r="D61" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E61" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I61" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O61" s="7"/>
     </row>
@@ -3433,166 +3442,166 @@
         <v>7</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D62" s="8">
-        <v>46085.366041666668</v>
+        <v>46077.368379629632</v>
       </c>
       <c r="E62" s="8">
-        <v>46085.366041666668</v>
+        <v>46077.368379629632</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I62" s="7">
-        <v>1423125</v>
+        <v>1422285</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
+        <v>3</v>
+      </c>
+      <c r="O62" s="7"/>
+    </row>
+    <row r="63" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A63" s="2"/>
+      <c r="B63" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E63" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I63" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10">
+        <v>3</v>
+      </c>
+      <c r="O63" s="7"/>
+    </row>
+    <row r="64" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A64" s="2"/>
+      <c r="B64" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="8">
+        <v>46085.366041666668</v>
+      </c>
+      <c r="E64" s="8">
+        <v>46085.366041666668</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I64" s="7">
+        <v>1423125</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10">
         <v>5</v>
       </c>
-      <c r="O62" s="7"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A63" s="4"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="9">
+      <c r="O64" s="7"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" s="4"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="9">
         <v>0</v>
       </c>
-      <c r="N63" s="9">
-        <v>250</v>
-      </c>
-      <c r="O63" s="9">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="3" t="s">
+      <c r="N65" s="9">
+        <v>260</v>
+      </c>
+      <c r="O65" s="9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B66" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="12"/>
-      <c r="M64" s="12"/>
-      <c r="N64" s="12"/>
-      <c r="O64" s="12"/>
-    </row>
-    <row r="65" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A65" s="2"/>
-      <c r="B65" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="E65" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I65" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K65" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="L65" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10">
-        <v>3</v>
-      </c>
-      <c r="O65" s="7"/>
-    </row>
-    <row r="66" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A66" s="2"/>
-      <c r="B66" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D66" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E66" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I66" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="L66" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10">
-        <v>1</v>
-      </c>
-      <c r="O66" s="7"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
     </row>
     <row r="67" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
@@ -3600,38 +3609,38 @@
         <v>4</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D67" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E67" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I67" s="7">
-        <v>1406206</v>
+        <v>1386388</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3641,38 +3650,38 @@
         <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D68" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E68" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I68" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3682,38 +3691,38 @@
         <v>4</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D69" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E69" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I69" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3723,38 +3732,38 @@
         <v>4</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D70" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E70" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I70" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3764,38 +3773,38 @@
         <v>4</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D71" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E71" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I71" s="7">
         <v>1411990</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3805,34 +3814,34 @@
         <v>4</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D72" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E72" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I72" s="7">
         <v>1411990</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
@@ -3846,38 +3855,38 @@
         <v>4</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D73" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E73" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I73" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3890,35 +3899,35 @@
         <v>41</v>
       </c>
       <c r="D74" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E74" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I74" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3928,239 +3937,239 @@
         <v>4</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D75" s="8">
-        <v>46084.883263888885</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E75" s="8">
-        <v>46084.883263888885</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I75" s="7">
-        <v>1428327</v>
+        <v>1410767</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O75" s="7"/>
     </row>
     <row r="76" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D76" s="8">
-        <v>46028.907905092594</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E76" s="8">
-        <v>46028.907905092594</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I76" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O76" s="7"/>
     </row>
     <row r="77" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D77" s="8">
-        <v>46029.6719212963</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E77" s="8">
-        <v>46029.6719212963</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I77" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O77" s="7"/>
     </row>
     <row r="78" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D78" s="8">
-        <v>46034.72855324074</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="E78" s="8">
-        <v>46034.72855324074</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I78" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78" s="7"/>
     </row>
     <row r="79" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D79" s="8">
-        <v>46037.838958333334</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="E79" s="8">
-        <v>46037.838958333334</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I79" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D80" s="8">
-        <v>46042.727754629632</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="E80" s="8">
-        <v>46042.727754629632</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I80" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
@@ -4171,37 +4180,37 @@
     <row r="81" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D81" s="8">
-        <v>46043.627881944441</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="E81" s="8">
-        <v>46043.627881944441</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I81" s="7">
-        <v>1410339</v>
+        <v>1427431</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
@@ -4215,38 +4224,38 @@
         <v>5</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D82" s="8">
-        <v>46052.626018518517</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E82" s="8">
-        <v>46052.626018518517</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I82" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L82" s="7" t="s">
         <v>116</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4256,38 +4265,38 @@
         <v>5</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="D83" s="8">
-        <v>46053.632291666669</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E83" s="8">
-        <v>46053.632291666669</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I83" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L83" s="7" t="s">
         <v>116</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4297,38 +4306,38 @@
         <v>5</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D84" s="8">
-        <v>46071.601446759261</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E84" s="8">
-        <v>46071.601446759261</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I84" s="7">
-        <v>1418251</v>
+        <v>1394721</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4338,38 +4347,38 @@
         <v>5</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D85" s="8">
-        <v>46076.679282407407</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E85" s="8">
-        <v>46076.679282407407</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I85" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4379,38 +4388,38 @@
         <v>5</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D86" s="8">
-        <v>46077.591944444444</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E86" s="8">
-        <v>46077.591944444444</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I86" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O86" s="7"/>
     </row>
@@ -4420,38 +4429,38 @@
         <v>5</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D87" s="8">
-        <v>46077.861296296294</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E87" s="8">
-        <v>46077.861296296294</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I87" s="7">
-        <v>1422511</v>
+        <v>1410339</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O87" s="7"/>
     </row>
@@ -4461,198 +4470,198 @@
         <v>5</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D88" s="8">
-        <v>46086.860844907409</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E88" s="8">
-        <v>46086.860844907409</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I88" s="7">
-        <v>1428373</v>
+        <v>1411706</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O88" s="7"/>
     </row>
     <row r="89" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D89" s="8">
-        <v>46027.633611111109</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E89" s="8">
-        <v>46027.633611111109</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I89" s="7">
-        <v>1404289</v>
+        <v>1411708</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O89" s="7"/>
     </row>
     <row r="90" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D90" s="8">
-        <v>46029.802372685182</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E90" s="8">
-        <v>46029.802372685182</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I90" s="7">
-        <v>1394724</v>
+        <v>1418251</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>111</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O90" s="7"/>
     </row>
     <row r="91" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D91" s="8">
-        <v>46030.908472222225</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E91" s="8">
-        <v>46030.908472222225</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I91" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K91" s="5" t="s">
         <v>111</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O91" s="7"/>
     </row>
     <row r="92" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D92" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E92" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I92" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K92" s="5" t="s">
         <v>111</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
@@ -4663,82 +4672,82 @@
     <row r="93" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D93" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E93" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I93" s="7">
-        <v>1422286</v>
+        <v>1422511</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K93" s="5" t="s">
         <v>111</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O93" s="7"/>
     </row>
     <row r="94" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D94" s="8">
-        <v>46078.867326388892</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="E94" s="8">
-        <v>46078.867326388892</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I94" s="7">
-        <v>1422286</v>
+        <v>1428373</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O94" s="7"/>
     </row>
@@ -4748,38 +4757,38 @@
         <v>6</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D95" s="8">
-        <v>46080.639293981483</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E95" s="8">
-        <v>46080.639293981483</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I95" s="7">
-        <v>1422285</v>
+        <v>1404289</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4789,38 +4798,38 @@
         <v>6</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D96" s="8">
-        <v>46080.716932870368</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E96" s="8">
-        <v>46080.716932870368</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I96" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>96</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O96" s="7"/>
     </row>
@@ -4830,38 +4839,38 @@
         <v>6</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D97" s="8">
-        <v>46080.740543981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E97" s="8">
-        <v>46080.740543981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I97" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>96</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O97" s="7"/>
     </row>
@@ -4871,38 +4880,38 @@
         <v>6</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D98" s="8">
-        <v>46081.588483796295</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E98" s="8">
-        <v>46081.588483796295</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I98" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J98" s="5" t="s">
         <v>96</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O98" s="7"/>
     </row>
@@ -4912,116 +4921,116 @@
         <v>6</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D99" s="8">
-        <v>46083.87841435185</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E99" s="8">
-        <v>46083.87841435185</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I99" s="7">
-        <v>1422283</v>
+        <v>1422286</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="O99" s="7"/>
     </row>
     <row r="100" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D100" s="8">
-        <v>46024.795127314814</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E100" s="8">
-        <v>46024.795127314814</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I100" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O100" s="7"/>
     </row>
     <row r="101" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D101" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E101" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I101" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
@@ -5032,242 +5041,242 @@
     <row r="102" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D102" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E102" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I102" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O102" s="7"/>
     </row>
     <row r="103" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D103" s="8">
-        <v>46028.866898148146</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E103" s="8">
-        <v>46028.866898148146</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I103" s="7">
-        <v>1402956</v>
+        <v>1422285</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O103" s="7"/>
     </row>
     <row r="104" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D104" s="8">
-        <v>46034.751261574071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E104" s="8">
-        <v>46034.751261574071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I104" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M104" s="10"/>
       <c r="N104" s="10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O104" s="7"/>
     </row>
     <row r="105" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D105" s="8">
-        <v>46062.904895833337</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E105" s="8">
-        <v>46062.904895833337</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I105" s="7">
-        <v>1412987</v>
+        <v>1422283</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M105" s="10"/>
       <c r="N105" s="10">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="O105" s="7"/>
     </row>
     <row r="106" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D106" s="8">
-        <v>46063.874467592592</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="E106" s="8">
-        <v>46063.874467592592</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I106" s="7">
-        <v>1412987</v>
+        <v>1422282</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M106" s="10"/>
       <c r="N106" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O106" s="7"/>
     </row>
     <row r="107" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D107" s="8">
-        <v>46067.906875000001</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="E107" s="8">
-        <v>46067.906875000001</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I107" s="7">
-        <v>1411991</v>
+        <v>1422282</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10">
@@ -5278,41 +5287,41 @@
     <row r="108" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D108" s="8">
-        <v>46069.700543981482</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="E108" s="8">
-        <v>46069.700543981482</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I108" s="7">
-        <v>1411991</v>
+        <v>1422282</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M108" s="10"/>
       <c r="N108" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O108" s="7"/>
     </row>
@@ -5322,38 +5331,38 @@
         <v>7</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D109" s="8">
-        <v>46077.65824074074</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E109" s="8">
-        <v>46077.65824074074</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I109" s="7">
-        <v>1422285</v>
+        <v>1398335</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K109" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M109" s="10"/>
       <c r="N109" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O109" s="7"/>
     </row>
@@ -5363,38 +5372,38 @@
         <v>7</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D110" s="8">
-        <v>46078.881018518521</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E110" s="8">
-        <v>46078.881018518521</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I110" s="7">
-        <v>1423123</v>
+        <v>1398335</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M110" s="10"/>
       <c r="N110" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O110" s="7"/>
     </row>
@@ -5404,87 +5413,456 @@
         <v>7</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D111" s="8">
-        <v>46079.901782407411</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E111" s="8">
-        <v>46079.901782407411</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I111" s="7">
-        <v>1423123</v>
+        <v>1398335</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M111" s="10"/>
       <c r="N111" s="10">
+        <v>5</v>
+      </c>
+      <c r="O111" s="7"/>
+    </row>
+    <row r="112" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A112" s="2"/>
+      <c r="B112" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" s="8">
+        <v>46028.866898148146</v>
+      </c>
+      <c r="E112" s="8">
+        <v>46028.866898148146</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I112" s="7">
+        <v>1402956</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L112" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M112" s="10"/>
+      <c r="N112" s="10">
+        <v>2</v>
+      </c>
+      <c r="O112" s="7"/>
+    </row>
+    <row r="113" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A113" s="2"/>
+      <c r="B113" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" s="8">
+        <v>46034.751261574071</v>
+      </c>
+      <c r="E113" s="8">
+        <v>46034.751261574071</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I113" s="7">
+        <v>1404958</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K113" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L113" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M113" s="10"/>
+      <c r="N113" s="10">
+        <v>7</v>
+      </c>
+      <c r="O113" s="7"/>
+    </row>
+    <row r="114" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A114" s="2"/>
+      <c r="B114" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="8">
+        <v>46062.904895833337</v>
+      </c>
+      <c r="E114" s="8">
+        <v>46062.904895833337</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I114" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K114" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M114" s="10"/>
+      <c r="N114" s="10">
         <v>1</v>
       </c>
-      <c r="O111" s="7"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A112" s="4"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="M112" s="9">
+      <c r="O114" s="7"/>
+    </row>
+    <row r="115" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A115" s="2"/>
+      <c r="B115" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D115" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="E115" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H115" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I115" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J115" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K115" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L115" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M115" s="10"/>
+      <c r="N115" s="10">
+        <v>5</v>
+      </c>
+      <c r="O115" s="7"/>
+    </row>
+    <row r="116" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A116" s="2"/>
+      <c r="B116" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D116" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E116" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I116" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J116" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K116" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L116" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="M116" s="10"/>
+      <c r="N116" s="10">
+        <v>3</v>
+      </c>
+      <c r="O116" s="7"/>
+    </row>
+    <row r="117" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A117" s="2"/>
+      <c r="B117" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D117" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E117" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I117" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J117" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K117" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L117" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="M117" s="10"/>
+      <c r="N117" s="10">
+        <v>10</v>
+      </c>
+      <c r="O117" s="7"/>
+    </row>
+    <row r="118" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A118" s="2"/>
+      <c r="B118" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D118" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E118" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I118" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J118" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K118" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L118" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M118" s="10"/>
+      <c r="N118" s="10">
+        <v>1</v>
+      </c>
+      <c r="O118" s="7"/>
+    </row>
+    <row r="119" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A119" s="2"/>
+      <c r="B119" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D119" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E119" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H119" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I119" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J119" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K119" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L119" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M119" s="10"/>
+      <c r="N119" s="10">
+        <v>1</v>
+      </c>
+      <c r="O119" s="7"/>
+    </row>
+    <row r="120" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A120" s="2"/>
+      <c r="B120" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D120" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E120" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I120" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K120" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L120" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M120" s="10"/>
+      <c r="N120" s="10">
+        <v>1</v>
+      </c>
+      <c r="O120" s="7"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A121" s="4"/>
+      <c r="B121" s="6"/>
+      <c r="C121" s="6"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="6"/>
+      <c r="H121" s="6"/>
+      <c r="I121" s="6"/>
+      <c r="J121" s="6"/>
+      <c r="K121" s="6"/>
+      <c r="L121" s="6"/>
+      <c r="M121" s="9">
         <v>0</v>
       </c>
-      <c r="N112" s="9">
-        <v>259</v>
-      </c>
-      <c r="O112" s="9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A113" s="4"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="9">
-        <v>106</v>
-      </c>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
-      <c r="M113" s="9">
+      <c r="N121" s="9">
+        <v>276</v>
+      </c>
+      <c r="O121" s="9">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A122" s="4"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+      <c r="H122" s="9">
+        <v>115</v>
+      </c>
+      <c r="I122" s="6"/>
+      <c r="J122" s="6"/>
+      <c r="K122" s="6"/>
+      <c r="L122" s="6"/>
+      <c r="M122" s="9">
         <v>0</v>
       </c>
-      <c r="N113" s="9">
-        <v>509</v>
-      </c>
-      <c r="O113" s="9">
-        <v>106</v>
+      <c r="N122" s="9">
+        <v>536</v>
+      </c>
+      <c r="O122" s="9">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -5494,7 +5872,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="B66:O66"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82CF9C91-22AF-482B-90BE-611DD5789D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0E391EA-A56F-48B9-9520-7B64DC52DE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC936890-B410-417B-B4F6-9A40F5669DC1}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{F9AB853C-A925-428B-B8B8-1C23A8D17946}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="131">
   <si>
     <t>Dados</t>
   </si>
@@ -136,6 +136,9 @@
     <t>03/02/2026</t>
   </si>
   <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
     <t>14/01/2026</t>
   </si>
   <si>
@@ -331,6 +334,9 @@
     <t xml:space="preserve">CI002027-ARIEL_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - ARIEL </t>
   </si>
   <si>
+    <t>CIPF002259MICKEYCLASS24 - COPO PEQUENO ROSCA 450 ML C/ IMPRESSÃO D</t>
+  </si>
+  <si>
     <t>CIPF002816-FITNESS_F-732 - CORPO GARRAFA FUN 600 ML - FITNESS F - I</t>
   </si>
   <si>
@@ -350,6 +356,9 @@
   </si>
   <si>
     <t xml:space="preserve">CI003141-EM-CASA-1389 - COPO CAFÉ FACETADO C/ IMPRESSÃO DIGITAL </t>
+  </si>
+  <si>
+    <t>CIPF002259-MINNIE-R-24 - COPO PEQUENO ROSCA 450 ML C/ IMPRESSÃO D</t>
   </si>
   <si>
     <t>Operador</t>
@@ -948,8 +957,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B3390D-5B1E-447F-A8A7-8114E061DE83}">
-  <dimension ref="A1:O122"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFD1972-6F35-4BEB-90E9-6D1C31695AC0}">
+  <dimension ref="A1:O127"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -980,14 +989,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -1001,40 +1010,40 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1073,25 +1082,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1114,25 +1123,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1155,25 +1164,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1196,25 +1205,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1237,25 +1246,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1278,25 +1287,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1319,25 +1328,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1360,25 +1369,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1401,25 +1410,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1442,25 +1451,25 @@
         <v>46086.442870370367</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I13" s="7">
         <v>1428327</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1483,25 +1492,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I14" s="7">
         <v>1402958</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1524,25 +1533,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1565,25 +1574,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1606,25 +1615,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I17" s="7">
         <v>1394721</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1647,25 +1656,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1688,25 +1697,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1729,25 +1738,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1770,25 +1779,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I21" s="7">
         <v>1410340</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1811,25 +1820,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I22" s="7">
         <v>1411706</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1852,25 +1861,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1893,25 +1902,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1934,25 +1943,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I25" s="7">
         <v>1411704</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1975,25 +1984,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I26" s="7">
         <v>1418256</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -2016,25 +2025,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2057,25 +2066,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2098,25 +2107,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I29" s="7">
         <v>1422511</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2139,25 +2148,25 @@
         <v>46083.272581018522</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I30" s="7">
         <v>1423124</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2180,25 +2189,25 @@
         <v>46085.323807870373</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I31" s="7">
         <v>1428373</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2221,25 +2230,25 @@
         <v>46085.344675925924</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I32" s="7">
         <v>1428373</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2262,25 +2271,25 @@
         <v>46086.434641203705</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I33" s="7">
         <v>1428373</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2303,25 +2312,25 @@
         <v>46027.4840625</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I34" s="7">
         <v>1404289</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2344,25 +2353,25 @@
         <v>46030.397997685184</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2385,25 +2394,25 @@
         <v>46030.408148148148</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2426,25 +2435,25 @@
         <v>46030.478854166664</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I37" s="7">
         <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2467,25 +2476,25 @@
         <v>46030.561284722222</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I38" s="7">
         <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2508,25 +2517,25 @@
         <v>46035.478368055556</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I39" s="7">
         <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
@@ -2549,25 +2558,25 @@
         <v>46043.385474537034</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I40" s="7">
         <v>1394724</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
@@ -2590,25 +2599,25 @@
         <v>46043.565196759257</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I41" s="7">
         <v>1394724</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
@@ -2631,25 +2640,25 @@
         <v>46069.559953703705</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I42" s="7">
         <v>1421099</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
@@ -2672,25 +2681,25 @@
         <v>46078.552407407406</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I43" s="7">
         <v>1422286</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
@@ -2713,25 +2722,25 @@
         <v>46080.522418981483</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I44" s="7">
         <v>1422285</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
@@ -2754,25 +2763,25 @@
         <v>46080.532164351855</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I45" s="7">
         <v>1422285</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2795,25 +2804,25 @@
         <v>46083.531342592592</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I46" s="7">
         <v>1422283</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2836,25 +2845,25 @@
         <v>46085.365902777776</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I47" s="7">
         <v>1422283</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
@@ -2877,25 +2886,25 @@
         <v>46086.317847222221</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I48" s="7">
         <v>1428242</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
@@ -2918,25 +2927,25 @@
         <v>46087.292048611111</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I49" s="7">
         <v>1422282</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
@@ -2959,25 +2968,25 @@
         <v>46087.575972222221</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I50" s="7">
         <v>1422282</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -3000,25 +3009,25 @@
         <v>46035.47824074074</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I51" s="7">
         <v>1404958</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
@@ -3041,25 +3050,25 @@
         <v>46043.385196759256</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I52" s="7">
         <v>1405794</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
@@ -3082,25 +3091,25 @@
         <v>46043.385289351849</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I53" s="7">
         <v>1405794</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
@@ -3123,25 +3132,25 @@
         <v>46043.441296296296</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I54" s="7">
         <v>1405794</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
@@ -3164,25 +3173,25 @@
         <v>46044.570300925923</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I55" s="7">
         <v>1405794</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
@@ -3205,25 +3214,25 @@
         <v>46050.574884259258</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I56" s="7">
         <v>1411351</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
@@ -3246,25 +3255,25 @@
         <v>46051.280300925922</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I57" s="7">
         <v>1411352</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
@@ -3287,25 +3296,25 @@
         <v>46056.33489583333</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I58" s="7">
         <v>1410338</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
@@ -3328,25 +3337,25 @@
         <v>46062.345243055555</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I59" s="7">
         <v>1412987</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
@@ -3369,25 +3378,25 @@
         <v>46064.292500000003</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I60" s="7">
         <v>1412987</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
@@ -3410,25 +3419,25 @@
         <v>46073.402627314812</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I61" s="7">
         <v>1421099</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
@@ -3451,25 +3460,25 @@
         <v>46077.368379629632</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I62" s="7">
         <v>1422285</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
@@ -3492,25 +3501,25 @@
         <v>46077.554594907408</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I63" s="7">
         <v>1422285</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
@@ -3533,25 +3542,25 @@
         <v>46085.366041666668</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I64" s="7">
         <v>1423125</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
@@ -3559,90 +3568,90 @@
       </c>
       <c r="O64" s="7"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A65" s="4"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="9">
+    <row r="65" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A65" s="2"/>
+      <c r="B65" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" s="8">
+        <v>46090.39471064815</v>
+      </c>
+      <c r="E65" s="8">
+        <v>46090.39471064815</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I65" s="7">
+        <v>1410769</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10">
+        <v>1</v>
+      </c>
+      <c r="O65" s="7"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A66" s="4"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="9">
         <v>0</v>
       </c>
-      <c r="N65" s="9">
-        <v>260</v>
-      </c>
-      <c r="O65" s="9">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
+      <c r="N66" s="9">
+        <v>261</v>
+      </c>
+      <c r="O66" s="9">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B67" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="12"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12"/>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12"/>
-      <c r="O66" s="12"/>
-    </row>
-    <row r="67" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A67" s="2"/>
-      <c r="B67" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D67" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="E67" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I67" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K67" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="L67" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10">
-        <v>3</v>
-      </c>
-      <c r="O67" s="7"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+      <c r="O67" s="12"/>
     </row>
     <row r="68" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
@@ -3653,35 +3662,35 @@
         <v>31</v>
       </c>
       <c r="D68" s="8">
-        <v>46027.694131944445</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E68" s="8">
-        <v>46027.694131944445</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I68" s="7">
         <v>1386388</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3691,38 +3700,38 @@
         <v>4</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D69" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E69" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I69" s="7">
-        <v>1406206</v>
+        <v>1386388</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3735,35 +3744,35 @@
         <v>39</v>
       </c>
       <c r="D70" s="8">
-        <v>46059.905682870369</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E70" s="8">
-        <v>46059.905682870369</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I70" s="7">
-        <v>1411984</v>
+        <v>1406206</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3773,38 +3782,38 @@
         <v>4</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D71" s="8">
-        <v>46064.60796296296</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E71" s="8">
-        <v>46064.60796296296</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I71" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3814,34 +3823,34 @@
         <v>4</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D72" s="8">
-        <v>46065.655185185184</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E72" s="8">
-        <v>46065.655185185184</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I72" s="7">
         <v>1411990</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
@@ -3858,35 +3867,35 @@
         <v>41</v>
       </c>
       <c r="D73" s="8">
-        <v>46066.613657407404</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E73" s="8">
-        <v>46066.613657407404</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I73" s="7">
         <v>1411990</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3896,38 +3905,38 @@
         <v>4</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D74" s="8">
-        <v>46066.670127314814</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E74" s="8">
-        <v>46066.670127314814</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I74" s="7">
         <v>1411990</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3940,35 +3949,35 @@
         <v>42</v>
       </c>
       <c r="D75" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E75" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I75" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3981,35 +3990,35 @@
         <v>43</v>
       </c>
       <c r="D76" s="8">
-        <v>46084.877986111111</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E76" s="8">
-        <v>46084.877986111111</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I76" s="7">
-        <v>1428327</v>
+        <v>1410767</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -4019,79 +4028,79 @@
         <v>4</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D77" s="8">
-        <v>46084.883263888885</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E77" s="8">
-        <v>46084.883263888885</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I77" s="7">
         <v>1428327</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O77" s="7"/>
     </row>
     <row r="78" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D78" s="8">
-        <v>46088.746967592589</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E78" s="8">
-        <v>46088.746967592589</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I78" s="7">
-        <v>1427431</v>
+        <v>1428327</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4101,19 +4110,19 @@
         <v>9</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D79" s="8">
-        <v>46088.837569444448</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="E79" s="8">
-        <v>46088.837569444448</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>79</v>
@@ -4122,17 +4131,17 @@
         <v>1427431</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4142,34 +4151,34 @@
         <v>9</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D80" s="8">
-        <v>46088.841886574075</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="E80" s="8">
-        <v>46088.841886574075</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I80" s="7">
         <v>1427431</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
@@ -4183,34 +4192,34 @@
         <v>9</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D81" s="8">
-        <v>46088.849849537037</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="E81" s="8">
-        <v>46088.849849537037</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I81" s="7">
         <v>1427431</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
@@ -4221,82 +4230,82 @@
     <row r="82" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D82" s="8">
-        <v>46028.907905092594</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="E82" s="8">
-        <v>46028.907905092594</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I82" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O82" s="7"/>
     </row>
     <row r="83" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D83" s="8">
-        <v>46029.6719212963</v>
+        <v>46090.828055555554</v>
       </c>
       <c r="E83" s="8">
-        <v>46029.6719212963</v>
+        <v>46090.828055555554</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I83" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4306,38 +4315,38 @@
         <v>5</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D84" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E84" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I84" s="7">
         <v>1394721</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4347,38 +4356,38 @@
         <v>5</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D85" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E85" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I85" s="7">
         <v>1394721</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4388,38 +4397,38 @@
         <v>5</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D86" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E86" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I86" s="7">
         <v>1394721</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O86" s="7"/>
     </row>
@@ -4429,38 +4438,38 @@
         <v>5</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D87" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E87" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I87" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O87" s="7"/>
     </row>
@@ -4473,35 +4482,35 @@
         <v>49</v>
       </c>
       <c r="D88" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E88" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I88" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>89</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>119</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O88" s="7"/>
     </row>
@@ -4511,38 +4520,38 @@
         <v>5</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D89" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E89" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I89" s="7">
-        <v>1411708</v>
+        <v>1410339</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L89" s="7" t="s">
         <v>119</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O89" s="7"/>
     </row>
@@ -4555,35 +4564,35 @@
         <v>50</v>
       </c>
       <c r="D90" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E90" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I90" s="7">
-        <v>1418251</v>
+        <v>1411706</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" s="7"/>
     </row>
@@ -4593,38 +4602,38 @@
         <v>5</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D91" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E91" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I91" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O91" s="7"/>
     </row>
@@ -4634,38 +4643,38 @@
         <v>5</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D92" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E92" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I92" s="7">
-        <v>1422511</v>
+        <v>1418251</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O92" s="7"/>
     </row>
@@ -4675,38 +4684,38 @@
         <v>5</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="D93" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E93" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I93" s="7">
         <v>1422511</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O93" s="7"/>
     </row>
@@ -4716,116 +4725,116 @@
         <v>5</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D94" s="8">
-        <v>46086.860844907409</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E94" s="8">
-        <v>46086.860844907409</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I94" s="7">
-        <v>1428373</v>
+        <v>1422511</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O94" s="7"/>
     </row>
     <row r="95" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D95" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E95" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I95" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K95" s="5" t="s">
         <v>114</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O95" s="7"/>
     </row>
     <row r="96" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D96" s="8">
-        <v>46029.802372685182</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="E96" s="8">
-        <v>46029.802372685182</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I96" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
@@ -4839,38 +4848,38 @@
         <v>6</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D97" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E97" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>79</v>
       </c>
       <c r="I97" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>96</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O97" s="7"/>
     </row>
@@ -4880,19 +4889,19 @@
         <v>6</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D98" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E98" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>79</v>
@@ -4901,17 +4910,17 @@
         <v>1394724</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O98" s="7"/>
     </row>
@@ -4921,38 +4930,38 @@
         <v>6</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="D99" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E99" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I99" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O99" s="7"/>
     </row>
@@ -4962,34 +4971,34 @@
         <v>6</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D100" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E100" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I100" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
@@ -5003,38 +5012,38 @@
         <v>6</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D101" s="8">
-        <v>46080.639293981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E101" s="8">
-        <v>46080.639293981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I101" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>99</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O101" s="7"/>
     </row>
@@ -5044,38 +5053,38 @@
         <v>6</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D102" s="8">
-        <v>46080.716932870368</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E102" s="8">
-        <v>46080.716932870368</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I102" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>99</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O102" s="7"/>
     </row>
@@ -5088,35 +5097,35 @@
         <v>34</v>
       </c>
       <c r="D103" s="8">
-        <v>46080.740543981483</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E103" s="8">
-        <v>46080.740543981483</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I103" s="7">
         <v>1422285</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O103" s="7"/>
     </row>
@@ -5126,34 +5135,34 @@
         <v>6</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D104" s="8">
-        <v>46081.588483796295</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E104" s="8">
-        <v>46081.588483796295</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I104" s="7">
         <v>1422285</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M104" s="10"/>
       <c r="N104" s="10">
@@ -5167,38 +5176,38 @@
         <v>6</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D105" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E105" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I105" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M105" s="10"/>
       <c r="N105" s="10">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="O105" s="7"/>
     </row>
@@ -5208,38 +5217,38 @@
         <v>6</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D106" s="8">
-        <v>46087.689409722225</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E106" s="8">
-        <v>46087.689409722225</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I106" s="7">
-        <v>1422282</v>
+        <v>1422285</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="M106" s="10"/>
       <c r="N106" s="10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O106" s="7"/>
     </row>
@@ -5249,38 +5258,38 @@
         <v>6</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D107" s="8">
-        <v>46088.641435185185</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E107" s="8">
-        <v>46088.641435185185</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I107" s="7">
-        <v>1422282</v>
+        <v>1422283</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>84</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="O107" s="7"/>
     </row>
@@ -5290,19 +5299,19 @@
         <v>6</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D108" s="8">
-        <v>46088.69903935185</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="E108" s="8">
-        <v>46088.69903935185</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>79</v>
@@ -5311,181 +5320,181 @@
         <v>1422282</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M108" s="10"/>
       <c r="N108" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O108" s="7"/>
     </row>
     <row r="109" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D109" s="8">
-        <v>46024.795127314814</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="E109" s="8">
-        <v>46024.795127314814</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>79</v>
       </c>
       <c r="I109" s="7">
-        <v>1398335</v>
+        <v>1422282</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="K109" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="M109" s="10"/>
       <c r="N109" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O109" s="7"/>
     </row>
     <row r="110" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D110" s="8">
-        <v>46024.795277777775</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="E110" s="8">
-        <v>46024.795277777775</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I110" s="7">
-        <v>1398335</v>
+        <v>1422282</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="M110" s="10"/>
       <c r="N110" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O110" s="7"/>
     </row>
     <row r="111" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D111" s="8">
-        <v>46024.900324074071</v>
+        <v>46090.906782407408</v>
       </c>
       <c r="E111" s="8">
-        <v>46024.900324074071</v>
+        <v>46090.906782407408</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>79</v>
       </c>
       <c r="I111" s="7">
-        <v>1398335</v>
+        <v>1428249</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="M111" s="10"/>
       <c r="N111" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O111" s="7"/>
     </row>
     <row r="112" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D112" s="8">
-        <v>46028.866898148146</v>
+        <v>46090.910081018519</v>
       </c>
       <c r="E112" s="8">
-        <v>46028.866898148146</v>
+        <v>46090.910081018519</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>79</v>
       </c>
       <c r="I112" s="7">
-        <v>1402956</v>
+        <v>1428249</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M112" s="10"/>
       <c r="N112" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O112" s="7"/>
     </row>
@@ -5495,38 +5504,38 @@
         <v>7</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D113" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E113" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I113" s="7">
-        <v>1404958</v>
+        <v>1398335</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K113" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M113" s="10"/>
       <c r="N113" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O113" s="7"/>
     </row>
@@ -5536,38 +5545,38 @@
         <v>7</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D114" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E114" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I114" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="K114" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M114" s="10"/>
       <c r="N114" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114" s="7"/>
     </row>
@@ -5580,31 +5589,31 @@
         <v>54</v>
       </c>
       <c r="D115" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E115" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I115" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J115" s="5" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="K115" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M115" s="10"/>
       <c r="N115" s="10">
@@ -5618,38 +5627,38 @@
         <v>7</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D116" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E116" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I116" s="7">
-        <v>1411991</v>
+        <v>1402956</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="K116" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O116" s="7"/>
     </row>
@@ -5659,38 +5668,38 @@
         <v>7</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D117" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E117" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I117" s="7">
-        <v>1411991</v>
+        <v>1404958</v>
       </c>
       <c r="J117" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K117" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M117" s="10"/>
       <c r="N117" s="10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O117" s="7"/>
     </row>
@@ -5700,34 +5709,34 @@
         <v>7</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D118" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E118" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I118" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10">
@@ -5741,38 +5750,38 @@
         <v>7</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D119" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E119" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I119" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J119" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K119" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M119" s="10"/>
       <c r="N119" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O119" s="7"/>
     </row>
@@ -5782,87 +5791,292 @@
         <v>7</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D120" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="E120" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I120" s="7">
-        <v>1423123</v>
+        <v>1411991</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M120" s="10"/>
       <c r="N120" s="10">
+        <v>3</v>
+      </c>
+      <c r="O120" s="7"/>
+    </row>
+    <row r="121" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A121" s="2"/>
+      <c r="B121" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D121" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E121" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H121" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I121" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J121" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="K121" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L121" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="M121" s="10"/>
+      <c r="N121" s="10">
+        <v>10</v>
+      </c>
+      <c r="O121" s="7"/>
+    </row>
+    <row r="122" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A122" s="2"/>
+      <c r="B122" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D122" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E122" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I122" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J122" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K122" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L122" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M122" s="10"/>
+      <c r="N122" s="10">
         <v>1</v>
       </c>
-      <c r="O120" s="7"/>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A121" s="4"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="9">
+      <c r="O122" s="7"/>
+    </row>
+    <row r="123" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A123" s="2"/>
+      <c r="B123" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E123" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I123" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J123" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K123" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L123" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M123" s="10"/>
+      <c r="N123" s="10">
+        <v>1</v>
+      </c>
+      <c r="O123" s="7"/>
+    </row>
+    <row r="124" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A124" s="2"/>
+      <c r="B124" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D124" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E124" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I124" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J124" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K124" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L124" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M124" s="10"/>
+      <c r="N124" s="10">
+        <v>1</v>
+      </c>
+      <c r="O124" s="7"/>
+    </row>
+    <row r="125" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A125" s="2"/>
+      <c r="B125" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D125" s="8">
+        <v>46090.910266203704</v>
+      </c>
+      <c r="E125" s="8">
+        <v>46090.910266203704</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H125" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I125" s="7">
+        <v>1410772</v>
+      </c>
+      <c r="J125" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K125" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L125" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M125" s="10"/>
+      <c r="N125" s="10">
+        <v>3</v>
+      </c>
+      <c r="O125" s="7"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A126" s="4"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="9">
         <v>0</v>
       </c>
-      <c r="N121" s="9">
-        <v>276</v>
-      </c>
-      <c r="O121" s="9">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A122" s="4"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="9">
-        <v>115</v>
-      </c>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
-      <c r="M122" s="9">
+      <c r="N126" s="9">
+        <v>284</v>
+      </c>
+      <c r="O126" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A127" s="4"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="9">
+        <v>120</v>
+      </c>
+      <c r="I127" s="6"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="9">
         <v>0</v>
       </c>
-      <c r="N122" s="9">
-        <v>536</v>
-      </c>
-      <c r="O122" s="9">
-        <v>115</v>
+      <c r="N127" s="9">
+        <v>545</v>
+      </c>
+      <c r="O127" s="9">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -5872,7 +6086,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B66:O66"/>
+    <mergeCell ref="B67:O67"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sala.impressao\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0E391EA-A56F-48B9-9520-7B64DC52DE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54995D57-35BB-4D0A-A3BD-79DB18D25DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{F9AB853C-A925-428B-B8B8-1C23A8D17946}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{9E52AEC1-A1FE-4F8F-9754-BF2E2E877660}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="133">
   <si>
     <t>Dados</t>
   </si>
@@ -157,6 +157,9 @@
     <t>03/03/2026</t>
   </si>
   <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
     <t>07/03/2026</t>
   </si>
   <si>
@@ -341,6 +344,9 @@
   </si>
   <si>
     <t>CIPF002259-LIMAO-24 - COPO PEQUENO ROSCA 450 ML C/ IMPRESSÃO D</t>
+  </si>
+  <si>
+    <t>CIPF002327-AMC-LAV-24 - GARRAFA CILINDRICA DEC 970ML - IMPRESSÃO</t>
   </si>
   <si>
     <t>CI002027-MICKEYFUTEBOL24 - CORPO GARRAFA RETRÔ 500ML SOPRO - IMPRES</t>
@@ -957,8 +963,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFD1972-6F35-4BEB-90E9-6D1C31695AC0}">
-  <dimension ref="A1:O127"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C14F77FA-7D25-4004-BCC3-20B5CF83F704}">
+  <dimension ref="A1:O135"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -989,14 +995,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -1010,40 +1016,40 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1082,25 +1088,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1123,25 +1129,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1164,25 +1170,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1205,25 +1211,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1246,25 +1252,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1287,25 +1293,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1328,25 +1334,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1369,25 +1375,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1410,25 +1416,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1451,25 +1457,25 @@
         <v>46086.442870370367</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I13" s="7">
         <v>1428327</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1492,25 +1498,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" s="7">
         <v>1402958</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1533,25 +1539,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1574,25 +1580,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1615,25 +1621,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" s="7">
         <v>1394721</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1656,25 +1662,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1697,25 +1703,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1738,25 +1744,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1779,25 +1785,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I21" s="7">
         <v>1410340</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1820,25 +1826,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I22" s="7">
         <v>1411706</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1861,25 +1867,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1902,25 +1908,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1943,25 +1949,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I25" s="7">
         <v>1411704</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1984,25 +1990,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I26" s="7">
         <v>1418256</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -2025,25 +2031,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2066,25 +2072,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2107,25 +2113,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I29" s="7">
         <v>1422511</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2148,25 +2154,25 @@
         <v>46083.272581018522</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I30" s="7">
         <v>1423124</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2189,25 +2195,25 @@
         <v>46085.323807870373</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I31" s="7">
         <v>1428373</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2230,25 +2236,25 @@
         <v>46085.344675925924</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I32" s="7">
         <v>1428373</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2271,25 +2277,25 @@
         <v>46086.434641203705</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I33" s="7">
         <v>1428373</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2312,25 +2318,25 @@
         <v>46027.4840625</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I34" s="7">
         <v>1404289</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2353,25 +2359,25 @@
         <v>46030.397997685184</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2394,25 +2400,25 @@
         <v>46030.408148148148</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2435,25 +2441,25 @@
         <v>46030.478854166664</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I37" s="7">
         <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2476,25 +2482,25 @@
         <v>46030.561284722222</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I38" s="7">
         <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2517,25 +2523,25 @@
         <v>46035.478368055556</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I39" s="7">
         <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
@@ -2558,25 +2564,25 @@
         <v>46043.385474537034</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I40" s="7">
         <v>1394724</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
@@ -2599,25 +2605,25 @@
         <v>46043.565196759257</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I41" s="7">
         <v>1394724</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
@@ -2640,25 +2646,25 @@
         <v>46069.559953703705</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I42" s="7">
         <v>1421099</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
@@ -2681,25 +2687,25 @@
         <v>46078.552407407406</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I43" s="7">
         <v>1422286</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
@@ -2722,25 +2728,25 @@
         <v>46080.522418981483</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I44" s="7">
         <v>1422285</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
@@ -2763,25 +2769,25 @@
         <v>46080.532164351855</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I45" s="7">
         <v>1422285</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2804,25 +2810,25 @@
         <v>46083.531342592592</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I46" s="7">
         <v>1422283</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2845,25 +2851,25 @@
         <v>46085.365902777776</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I47" s="7">
         <v>1422283</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
@@ -2886,25 +2892,25 @@
         <v>46086.317847222221</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I48" s="7">
         <v>1428242</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
@@ -2927,25 +2933,25 @@
         <v>46087.292048611111</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I49" s="7">
         <v>1422282</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
@@ -2968,25 +2974,25 @@
         <v>46087.575972222221</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I50" s="7">
         <v>1422282</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -3009,25 +3015,25 @@
         <v>46035.47824074074</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I51" s="7">
         <v>1404958</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
@@ -3050,25 +3056,25 @@
         <v>46043.385196759256</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I52" s="7">
         <v>1405794</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
@@ -3091,25 +3097,25 @@
         <v>46043.385289351849</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I53" s="7">
         <v>1405794</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
@@ -3132,25 +3138,25 @@
         <v>46043.441296296296</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I54" s="7">
         <v>1405794</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
@@ -3173,25 +3179,25 @@
         <v>46044.570300925923</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I55" s="7">
         <v>1405794</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
@@ -3214,25 +3220,25 @@
         <v>46050.574884259258</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I56" s="7">
         <v>1411351</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
@@ -3255,25 +3261,25 @@
         <v>46051.280300925922</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I57" s="7">
         <v>1411352</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
@@ -3296,25 +3302,25 @@
         <v>46056.33489583333</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I58" s="7">
         <v>1410338</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
@@ -3337,25 +3343,25 @@
         <v>46062.345243055555</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I59" s="7">
         <v>1412987</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
@@ -3378,25 +3384,25 @@
         <v>46064.292500000003</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I60" s="7">
         <v>1412987</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
@@ -3419,25 +3425,25 @@
         <v>46073.402627314812</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I61" s="7">
         <v>1421099</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
@@ -3460,25 +3466,25 @@
         <v>46077.368379629632</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I62" s="7">
         <v>1422285</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
@@ -3501,25 +3507,25 @@
         <v>46077.554594907408</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I63" s="7">
         <v>1422285</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
@@ -3542,25 +3548,25 @@
         <v>46085.366041666668</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I64" s="7">
         <v>1423125</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
@@ -3583,25 +3589,25 @@
         <v>46090.39471064815</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I65" s="7">
         <v>1410769</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
@@ -3668,25 +3674,25 @@
         <v>46027.666331018518</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I68" s="7">
         <v>1386388</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
@@ -3709,25 +3715,25 @@
         <v>46027.694131944445</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I69" s="7">
         <v>1386388</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
@@ -3750,25 +3756,25 @@
         <v>46036.841574074075</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I70" s="7">
         <v>1406206</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
@@ -3791,25 +3797,25 @@
         <v>46059.905682870369</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I71" s="7">
         <v>1411984</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
@@ -3832,25 +3838,25 @@
         <v>46064.60796296296</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I72" s="7">
         <v>1411990</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
@@ -3873,25 +3879,25 @@
         <v>46065.655185185184</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I73" s="7">
         <v>1411990</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
@@ -3914,25 +3920,25 @@
         <v>46066.613657407404</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I74" s="7">
         <v>1411990</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
@@ -3955,25 +3961,25 @@
         <v>46066.670127314814</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I75" s="7">
         <v>1411990</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
@@ -3996,25 +4002,25 @@
         <v>46079.703912037039</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I76" s="7">
         <v>1410767</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
@@ -4037,25 +4043,25 @@
         <v>46084.877986111111</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I77" s="7">
         <v>1428327</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
@@ -4078,25 +4084,25 @@
         <v>46084.883263888885</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I78" s="7">
         <v>1428327</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
@@ -4107,78 +4113,78 @@
     <row r="79" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D79" s="8">
-        <v>46088.746967592589</v>
+        <v>46091.687349537038</v>
       </c>
       <c r="E79" s="8">
-        <v>46088.746967592589</v>
+        <v>46091.687349537038</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I79" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D80" s="8">
-        <v>46088.837569444448</v>
+        <v>46091.708692129629</v>
       </c>
       <c r="E80" s="8">
-        <v>46088.837569444448</v>
+        <v>46091.708692129629</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I80" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
@@ -4189,37 +4195,37 @@
     <row r="81" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D81" s="8">
-        <v>46088.841886574075</v>
+        <v>46091.738194444442</v>
       </c>
       <c r="E81" s="8">
-        <v>46088.841886574075</v>
+        <v>46091.738194444442</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I81" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
@@ -4233,19 +4239,19 @@
         <v>9</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D82" s="8">
-        <v>46088.849849537037</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="E82" s="8">
-        <v>46088.849849537037</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>80</v>
@@ -4254,17 +4260,17 @@
         <v>1427431</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4274,34 +4280,34 @@
         <v>9</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D83" s="8">
-        <v>46090.828055555554</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="E83" s="8">
-        <v>46090.828055555554</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I83" s="7">
         <v>1427431</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
@@ -4312,242 +4318,242 @@
     <row r="84" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D84" s="8">
-        <v>46028.907905092594</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="E84" s="8">
-        <v>46028.907905092594</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I84" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O84" s="7"/>
     </row>
     <row r="85" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D85" s="8">
-        <v>46029.6719212963</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="E85" s="8">
-        <v>46029.6719212963</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I85" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O85" s="7"/>
     </row>
     <row r="86" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D86" s="8">
-        <v>46034.72855324074</v>
+        <v>46090.828055555554</v>
       </c>
       <c r="E86" s="8">
-        <v>46034.72855324074</v>
+        <v>46090.828055555554</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I86" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O86" s="7"/>
     </row>
     <row r="87" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D87" s="8">
-        <v>46037.838958333334</v>
+        <v>46091.686921296299</v>
       </c>
       <c r="E87" s="8">
-        <v>46037.838958333334</v>
+        <v>46091.686921296299</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I87" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O87" s="7"/>
     </row>
     <row r="88" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D88" s="8">
-        <v>46042.727754629632</v>
+        <v>46091.72351851852</v>
       </c>
       <c r="E88" s="8">
-        <v>46042.727754629632</v>
+        <v>46091.72351851852</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I88" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O88" s="7"/>
     </row>
     <row r="89" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D89" s="8">
-        <v>46043.627881944441</v>
+        <v>46091.737939814811</v>
       </c>
       <c r="E89" s="8">
-        <v>46043.627881944441</v>
+        <v>46091.737939814811</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I89" s="7">
-        <v>1410339</v>
+        <v>1427431</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
@@ -4558,41 +4564,41 @@
     <row r="90" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D90" s="8">
-        <v>46052.626018518517</v>
+        <v>46091.838368055556</v>
       </c>
       <c r="E90" s="8">
-        <v>46052.626018518517</v>
+        <v>46091.838368055556</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I90" s="7">
-        <v>1411706</v>
+        <v>1427431</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O90" s="7"/>
     </row>
@@ -4602,38 +4608,38 @@
         <v>5</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D91" s="8">
-        <v>46053.632291666669</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E91" s="8">
-        <v>46053.632291666669</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I91" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O91" s="7"/>
     </row>
@@ -4643,38 +4649,38 @@
         <v>5</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D92" s="8">
-        <v>46071.601446759261</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E92" s="8">
-        <v>46071.601446759261</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I92" s="7">
-        <v>1418251</v>
+        <v>1394721</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O92" s="7"/>
     </row>
@@ -4684,38 +4690,38 @@
         <v>5</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D93" s="8">
-        <v>46076.679282407407</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E93" s="8">
-        <v>46076.679282407407</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I93" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O93" s="7"/>
     </row>
@@ -4725,38 +4731,38 @@
         <v>5</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D94" s="8">
-        <v>46077.591944444444</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E94" s="8">
-        <v>46077.591944444444</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I94" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O94" s="7"/>
     </row>
@@ -4766,38 +4772,38 @@
         <v>5</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D95" s="8">
-        <v>46077.861296296294</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E95" s="8">
-        <v>46077.861296296294</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I95" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4807,366 +4813,366 @@
         <v>5</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D96" s="8">
-        <v>46086.860844907409</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E96" s="8">
-        <v>46086.860844907409</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I96" s="7">
-        <v>1428373</v>
+        <v>1410339</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O96" s="7"/>
     </row>
     <row r="97" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D97" s="8">
-        <v>46027.633611111109</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E97" s="8">
-        <v>46027.633611111109</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I97" s="7">
-        <v>1404289</v>
+        <v>1411706</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O97" s="7"/>
     </row>
     <row r="98" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D98" s="8">
-        <v>46029.802372685182</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E98" s="8">
-        <v>46029.802372685182</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I98" s="7">
-        <v>1394724</v>
+        <v>1411708</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O98" s="7"/>
     </row>
     <row r="99" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D99" s="8">
-        <v>46030.908472222225</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E99" s="8">
-        <v>46030.908472222225</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I99" s="7">
-        <v>1394724</v>
+        <v>1418251</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O99" s="7"/>
     </row>
     <row r="100" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D100" s="8">
-        <v>46031.590057870373</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E100" s="8">
-        <v>46031.590057870373</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I100" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O100" s="7"/>
     </row>
     <row r="101" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D101" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E101" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I101" s="7">
-        <v>1422286</v>
+        <v>1422511</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O101" s="7"/>
     </row>
     <row r="102" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D102" s="8">
-        <v>46078.867326388892</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E102" s="8">
-        <v>46078.867326388892</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I102" s="7">
-        <v>1422286</v>
+        <v>1422511</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O102" s="7"/>
     </row>
     <row r="103" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D103" s="8">
-        <v>46080.639293981483</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="E103" s="8">
-        <v>46080.639293981483</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I103" s="7">
-        <v>1422285</v>
+        <v>1428373</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O103" s="7"/>
     </row>
     <row r="104" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D104" s="8">
-        <v>46080.716932870368</v>
+        <v>46091.867337962962</v>
       </c>
       <c r="E104" s="8">
-        <v>46080.716932870368</v>
+        <v>46091.867337962962</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I104" s="7">
-        <v>1422285</v>
+        <v>1428373</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M104" s="10"/>
       <c r="N104" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" s="7"/>
     </row>
@@ -5176,38 +5182,38 @@
         <v>6</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D105" s="8">
-        <v>46080.740543981483</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E105" s="8">
-        <v>46080.740543981483</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I105" s="7">
-        <v>1422285</v>
+        <v>1404289</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M105" s="10"/>
       <c r="N105" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O105" s="7"/>
     </row>
@@ -5217,38 +5223,38 @@
         <v>6</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D106" s="8">
-        <v>46081.588483796295</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E106" s="8">
-        <v>46081.588483796295</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I106" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M106" s="10"/>
       <c r="N106" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O106" s="7"/>
     </row>
@@ -5258,38 +5264,38 @@
         <v>6</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D107" s="8">
-        <v>46083.87841435185</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E107" s="8">
-        <v>46083.87841435185</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I107" s="7">
-        <v>1422283</v>
+        <v>1394724</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="O107" s="7"/>
     </row>
@@ -5299,38 +5305,38 @@
         <v>6</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D108" s="8">
-        <v>46087.689409722225</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E108" s="8">
-        <v>46087.689409722225</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I108" s="7">
-        <v>1422282</v>
+        <v>1394724</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L108" s="7" t="s">
         <v>121</v>
       </c>
       <c r="M108" s="10"/>
       <c r="N108" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O108" s="7"/>
     </row>
@@ -5340,38 +5346,38 @@
         <v>6</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D109" s="8">
-        <v>46088.641435185185</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E109" s="8">
-        <v>46088.641435185185</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I109" s="7">
-        <v>1422282</v>
+        <v>1422286</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K109" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M109" s="10"/>
       <c r="N109" s="10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O109" s="7"/>
     </row>
@@ -5381,38 +5387,38 @@
         <v>6</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D110" s="8">
-        <v>46088.69903935185</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E110" s="8">
-        <v>46088.69903935185</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I110" s="7">
-        <v>1422282</v>
+        <v>1422286</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M110" s="10"/>
       <c r="N110" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O110" s="7"/>
     </row>
@@ -5422,38 +5428,38 @@
         <v>6</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D111" s="8">
-        <v>46090.906782407408</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E111" s="8">
-        <v>46090.906782407408</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I111" s="7">
-        <v>1428249</v>
+        <v>1422285</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M111" s="10"/>
       <c r="N111" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O111" s="7"/>
     </row>
@@ -5463,34 +5469,34 @@
         <v>6</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D112" s="8">
-        <v>46090.910081018519</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E112" s="8">
-        <v>46090.910081018519</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I112" s="7">
-        <v>1428249</v>
+        <v>1422285</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M112" s="10"/>
       <c r="N112" s="10">
@@ -5501,242 +5507,242 @@
     <row r="113" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D113" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E113" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I113" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K113" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M113" s="10"/>
       <c r="N113" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O113" s="7"/>
     </row>
     <row r="114" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>54</v>
       </c>
       <c r="D114" s="8">
-        <v>46024.795277777775</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E114" s="8">
-        <v>46024.795277777775</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I114" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K114" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M114" s="10"/>
       <c r="N114" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114" s="7"/>
     </row>
     <row r="115" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D115" s="8">
-        <v>46024.900324074071</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E115" s="8">
-        <v>46024.900324074071</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I115" s="7">
-        <v>1398335</v>
+        <v>1422283</v>
       </c>
       <c r="J115" s="5" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K115" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M115" s="10"/>
       <c r="N115" s="10">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="O115" s="7"/>
     </row>
     <row r="116" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D116" s="8">
-        <v>46028.866898148146</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="E116" s="8">
-        <v>46028.866898148146</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I116" s="7">
-        <v>1402956</v>
+        <v>1422282</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K116" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O116" s="7"/>
     </row>
     <row r="117" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D117" s="8">
-        <v>46034.751261574071</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="E117" s="8">
-        <v>46034.751261574071</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I117" s="7">
-        <v>1404958</v>
+        <v>1422282</v>
       </c>
       <c r="J117" s="5" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="K117" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M117" s="10"/>
       <c r="N117" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O117" s="7"/>
     </row>
     <row r="118" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D118" s="8">
-        <v>46062.904895833337</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="E118" s="8">
-        <v>46062.904895833337</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I118" s="7">
-        <v>1412987</v>
+        <v>1422282</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10">
@@ -5747,82 +5753,82 @@
     <row r="119" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D119" s="8">
-        <v>46063.874467592592</v>
+        <v>46090.906782407408</v>
       </c>
       <c r="E119" s="8">
-        <v>46063.874467592592</v>
+        <v>46090.906782407408</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I119" s="7">
-        <v>1412987</v>
+        <v>1428249</v>
       </c>
       <c r="J119" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K119" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M119" s="10"/>
       <c r="N119" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O119" s="7"/>
     </row>
     <row r="120" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D120" s="8">
-        <v>46067.906875000001</v>
+        <v>46090.910081018519</v>
       </c>
       <c r="E120" s="8">
-        <v>46067.906875000001</v>
+        <v>46090.910081018519</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I120" s="7">
-        <v>1411991</v>
+        <v>1428249</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M120" s="10"/>
       <c r="N120" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O120" s="7"/>
     </row>
@@ -5832,38 +5838,38 @@
         <v>7</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D121" s="8">
-        <v>46069.700543981482</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E121" s="8">
-        <v>46069.700543981482</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I121" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K121" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="M121" s="10"/>
       <c r="N121" s="10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O121" s="7"/>
     </row>
@@ -5873,38 +5879,38 @@
         <v>7</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D122" s="8">
-        <v>46077.65824074074</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E122" s="8">
-        <v>46077.65824074074</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I122" s="7">
-        <v>1422285</v>
+        <v>1398335</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M122" s="10"/>
       <c r="N122" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O122" s="7"/>
     </row>
@@ -5914,38 +5920,38 @@
         <v>7</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D123" s="8">
-        <v>46078.881018518521</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E123" s="8">
-        <v>46078.881018518521</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I123" s="7">
-        <v>1423123</v>
+        <v>1398335</v>
       </c>
       <c r="J123" s="5" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="K123" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L123" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M123" s="10"/>
       <c r="N123" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O123" s="7"/>
     </row>
@@ -5955,38 +5961,38 @@
         <v>7</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D124" s="8">
-        <v>46079.901782407411</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E124" s="8">
-        <v>46079.901782407411</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I124" s="7">
-        <v>1423123</v>
+        <v>1402956</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K124" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M124" s="10"/>
       <c r="N124" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O124" s="7"/>
     </row>
@@ -5996,87 +6002,415 @@
         <v>7</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D125" s="8">
-        <v>46090.910266203704</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E125" s="8">
-        <v>46090.910266203704</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I125" s="7">
-        <v>1410772</v>
+        <v>1404958</v>
       </c>
       <c r="J125" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="K125" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L125" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M125" s="10"/>
       <c r="N125" s="10">
+        <v>7</v>
+      </c>
+      <c r="O125" s="7"/>
+    </row>
+    <row r="126" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A126" s="2"/>
+      <c r="B126" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" s="8">
+        <v>46062.904895833337</v>
+      </c>
+      <c r="E126" s="8">
+        <v>46062.904895833337</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H126" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I126" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K126" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L126" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M126" s="10"/>
+      <c r="N126" s="10">
+        <v>1</v>
+      </c>
+      <c r="O126" s="7"/>
+    </row>
+    <row r="127" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A127" s="2"/>
+      <c r="B127" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D127" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="E127" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H127" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I127" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J127" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K127" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L127" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M127" s="10"/>
+      <c r="N127" s="10">
+        <v>5</v>
+      </c>
+      <c r="O127" s="7"/>
+    </row>
+    <row r="128" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A128" s="2"/>
+      <c r="B128" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D128" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E128" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H128" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I128" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J128" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K128" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L128" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="M128" s="10"/>
+      <c r="N128" s="10">
         <v>3</v>
       </c>
-      <c r="O125" s="7"/>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A126" s="4"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6"/>
-      <c r="L126" s="6"/>
-      <c r="M126" s="9">
+      <c r="O128" s="7"/>
+    </row>
+    <row r="129" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A129" s="2"/>
+      <c r="B129" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D129" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E129" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I129" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J129" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K129" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L129" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="M129" s="10"/>
+      <c r="N129" s="10">
+        <v>10</v>
+      </c>
+      <c r="O129" s="7"/>
+    </row>
+    <row r="130" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A130" s="2"/>
+      <c r="B130" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D130" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E130" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I130" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J130" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K130" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L130" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="M130" s="10"/>
+      <c r="N130" s="10">
+        <v>1</v>
+      </c>
+      <c r="O130" s="7"/>
+    </row>
+    <row r="131" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A131" s="2"/>
+      <c r="B131" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E131" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I131" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J131" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K131" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L131" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M131" s="10"/>
+      <c r="N131" s="10">
+        <v>1</v>
+      </c>
+      <c r="O131" s="7"/>
+    </row>
+    <row r="132" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A132" s="2"/>
+      <c r="B132" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D132" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E132" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I132" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J132" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K132" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L132" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M132" s="10"/>
+      <c r="N132" s="10">
+        <v>1</v>
+      </c>
+      <c r="O132" s="7"/>
+    </row>
+    <row r="133" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A133" s="2"/>
+      <c r="B133" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D133" s="8">
+        <v>46090.910266203704</v>
+      </c>
+      <c r="E133" s="8">
+        <v>46090.910266203704</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H133" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I133" s="7">
+        <v>1410772</v>
+      </c>
+      <c r="J133" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K133" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L133" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M133" s="10"/>
+      <c r="N133" s="10">
+        <v>3</v>
+      </c>
+      <c r="O133" s="7"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A134" s="4"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="6"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="9">
         <v>0</v>
       </c>
-      <c r="N126" s="9">
-        <v>284</v>
-      </c>
-      <c r="O126" s="9">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A127" s="4"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="9">
-        <v>120</v>
-      </c>
-      <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
-      <c r="L127" s="6"/>
-      <c r="M127" s="9">
+      <c r="N134" s="9">
+        <v>315</v>
+      </c>
+      <c r="O134" s="9">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A135" s="4"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="9">
+        <v>128</v>
+      </c>
+      <c r="I135" s="6"/>
+      <c r="J135" s="6"/>
+      <c r="K135" s="6"/>
+      <c r="L135" s="6"/>
+      <c r="M135" s="9">
         <v>0</v>
       </c>
-      <c r="N127" s="9">
-        <v>545</v>
-      </c>
-      <c r="O127" s="9">
-        <v>120</v>
+      <c r="N135" s="9">
+        <v>576</v>
+      </c>
+      <c r="O135" s="9">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sala.impressao\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54995D57-35BB-4D0A-A3BD-79DB18D25DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6DFE4AE-9797-4347-9E50-26601CF1040B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{9E52AEC1-A1FE-4F8F-9754-BF2E2E877660}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{91E89078-AA4C-474D-B912-6FF611353892}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="136">
   <si>
     <t>Dados</t>
   </si>
@@ -37,6 +37,9 @@
     <t>28-CX-360G</t>
   </si>
   <si>
+    <t>29-CX-360G</t>
+  </si>
+  <si>
     <t>180- CX-360G</t>
   </si>
   <si>
@@ -49,9 +52,6 @@
     <t>Turno : 2</t>
   </si>
   <si>
-    <t>29-CX-360G</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
@@ -76,6 +76,12 @@
     <t>05/03/2026</t>
   </si>
   <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
     <t>06/01/2026</t>
   </si>
   <si>
@@ -289,6 +295,12 @@
     <t>CIPF002325-JARD-ENC_26-24 - GARRAFA CILINDRICA DEC 480ML - IMPRESSÃO</t>
   </si>
   <si>
+    <t>CIPF002327-AMC-LAV-24 - GARRAFA CILINDRICA DEC 970ML - IMPRESSÃO</t>
+  </si>
+  <si>
+    <t>CI002027-COPA_2026-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - IMPRES</t>
+  </si>
+  <si>
     <t>CI002027-FROZEN_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - FROZEN</t>
   </si>
   <si>
@@ -298,9 +310,6 @@
     <t>CIPF002325-HIDRATAN-1206 - GARRAFA CILINDRICA DEC 480ML - HIDRATANT</t>
   </si>
   <si>
-    <t>CI002027-COPA_2026-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - IMPRES</t>
-  </si>
-  <si>
     <t>CIPF002325-URSO_26-24 - GARRAFA CILINDRICA DEC 480ML - IMPRESSÃO</t>
   </si>
   <si>
@@ -346,7 +355,7 @@
     <t>CIPF002259-LIMAO-24 - COPO PEQUENO ROSCA 450 ML C/ IMPRESSÃO D</t>
   </si>
   <si>
-    <t>CIPF002327-AMC-LAV-24 - GARRAFA CILINDRICA DEC 970ML - IMPRESSÃO</t>
+    <t>CIPF002327-SAB-LAV-24 - GARRAFA CILINDRICA DEC 970ML - IMPRESSÃO</t>
   </si>
   <si>
     <t>CI002027-MICKEYFUTEBOL24 - CORPO GARRAFA RETRÔ 500ML SOPRO - IMPRES</t>
@@ -963,8 +972,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C14F77FA-7D25-4004-BCC3-20B5CF83F704}">
-  <dimension ref="A1:O135"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3AA45F3-C7AE-4783-97EB-8C6A289F7541}">
+  <dimension ref="A1:O142"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -995,14 +1004,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -1016,40 +1025,40 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1088,25 +1097,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1129,25 +1138,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1170,25 +1179,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1211,25 +1220,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1252,25 +1261,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1293,25 +1302,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1334,25 +1343,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1375,25 +1384,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1416,25 +1425,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1457,25 +1466,25 @@
         <v>46086.442870370367</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I13" s="7">
         <v>1428327</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1486,82 +1495,82 @@
     <row r="14" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="8">
-        <v>46028.331469907411</v>
+        <v>46092.58315972222</v>
       </c>
       <c r="E14" s="8">
-        <v>46028.331469907411</v>
+        <v>46092.58315972222</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I14" s="7">
-        <v>1402958</v>
+        <v>1423607</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="8">
-        <v>46030.306192129632</v>
+        <v>46093.440821759257</v>
       </c>
       <c r="E15" s="8">
-        <v>46030.306192129632</v>
+        <v>46093.440821759257</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I15" s="7">
-        <v>1394721</v>
+        <v>1423607</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O15" s="7"/>
     </row>
@@ -1571,116 +1580,116 @@
         <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" s="8">
-        <v>46031.443101851852</v>
+        <v>46092.583298611113</v>
       </c>
       <c r="E16" s="8">
-        <v>46031.443101851852</v>
+        <v>46092.583298611113</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I16" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="8">
-        <v>46035.530381944445</v>
+        <v>46028.331469907411</v>
       </c>
       <c r="E17" s="8">
-        <v>46035.530381944445</v>
+        <v>46028.331469907411</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I17" s="7">
-        <v>1394721</v>
+        <v>1402958</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D18" s="8">
-        <v>46046.391701388886</v>
+        <v>46030.306192129632</v>
       </c>
       <c r="E18" s="8">
-        <v>46046.391701388886</v>
+        <v>46030.306192129632</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I18" s="7">
-        <v>1410340</v>
+        <v>1394721</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1691,242 +1700,242 @@
     <row r="19" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D19" s="8">
-        <v>46046.516597222224</v>
+        <v>46031.443101851852</v>
       </c>
       <c r="E19" s="8">
-        <v>46046.516597222224</v>
+        <v>46031.443101851852</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I19" s="7">
-        <v>1410340</v>
+        <v>1394721</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="8">
-        <v>46048.278912037036</v>
+        <v>46035.530381944445</v>
       </c>
       <c r="E20" s="8">
-        <v>46048.278912037036</v>
+        <v>46035.530381944445</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I20" s="7">
-        <v>1410340</v>
+        <v>1394721</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" s="8">
-        <v>46051.403391203705</v>
+        <v>46046.391701388886</v>
       </c>
       <c r="E21" s="8">
-        <v>46051.403391203705</v>
+        <v>46046.391701388886</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I21" s="7">
         <v>1410340</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D22" s="8">
-        <v>46053.550381944442</v>
+        <v>46046.516597222224</v>
       </c>
       <c r="E22" s="8">
-        <v>46053.550381944442</v>
+        <v>46046.516597222224</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I22" s="7">
-        <v>1411706</v>
+        <v>1410340</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>124</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O22" s="7"/>
     </row>
     <row r="23" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D23" s="8">
-        <v>46057.413171296299</v>
+        <v>46048.278912037036</v>
       </c>
       <c r="E23" s="8">
-        <v>46057.413171296299</v>
+        <v>46048.278912037036</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I23" s="7">
-        <v>1411704</v>
+        <v>1410340</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O23" s="7"/>
     </row>
     <row r="24" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D24" s="8">
-        <v>46058.357476851852</v>
+        <v>46051.403391203705</v>
       </c>
       <c r="E24" s="8">
-        <v>46058.357476851852</v>
+        <v>46051.403391203705</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I24" s="7">
-        <v>1411704</v>
+        <v>1410340</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1937,78 +1946,78 @@
     <row r="25" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D25" s="8">
-        <v>46058.531793981485</v>
+        <v>46053.550381944442</v>
       </c>
       <c r="E25" s="8">
-        <v>46058.531793981485</v>
+        <v>46053.550381944442</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I25" s="7">
-        <v>1411704</v>
+        <v>1411706</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O25" s="7"/>
     </row>
     <row r="26" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="8">
-        <v>46067.433020833334</v>
+        <v>46057.413171296299</v>
       </c>
       <c r="E26" s="8">
-        <v>46067.433020833334</v>
+        <v>46057.413171296299</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I26" s="7">
-        <v>1418256</v>
+        <v>1411704</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -2019,78 +2028,78 @@
     <row r="27" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D27" s="8">
-        <v>46073.579664351855</v>
+        <v>46058.357476851852</v>
       </c>
       <c r="E27" s="8">
-        <v>46073.579664351855</v>
+        <v>46058.357476851852</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I27" s="7">
-        <v>1422511</v>
+        <v>1411704</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" s="8">
-        <v>46077.38318287037</v>
+        <v>46058.531793981485</v>
       </c>
       <c r="E28" s="8">
-        <v>46077.38318287037</v>
+        <v>46058.531793981485</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I28" s="7">
-        <v>1422511</v>
+        <v>1411704</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2101,37 +2110,37 @@
     <row r="29" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" s="8">
-        <v>46078.372766203705</v>
+        <v>46067.433020833334</v>
       </c>
       <c r="E29" s="8">
-        <v>46078.372766203705</v>
+        <v>46067.433020833334</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I29" s="7">
-        <v>1422511</v>
+        <v>1418256</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2142,78 +2151,78 @@
     <row r="30" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="8">
-        <v>46083.272581018522</v>
+        <v>46073.579664351855</v>
       </c>
       <c r="E30" s="8">
-        <v>46083.272581018522</v>
+        <v>46073.579664351855</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I30" s="7">
-        <v>1423124</v>
+        <v>1422511</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="8">
-        <v>46085.323807870373</v>
+        <v>46077.38318287037</v>
       </c>
       <c r="E31" s="8">
-        <v>46085.323807870373</v>
+        <v>46077.38318287037</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I31" s="7">
-        <v>1428373</v>
+        <v>1422511</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2224,82 +2233,82 @@
     <row r="32" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D32" s="8">
-        <v>46085.344675925924</v>
+        <v>46078.372766203705</v>
       </c>
       <c r="E32" s="8">
-        <v>46085.344675925924</v>
+        <v>46078.372766203705</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I32" s="7">
-        <v>1428373</v>
+        <v>1422511</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D33" s="8">
-        <v>46086.434641203705</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="E33" s="8">
-        <v>46086.434641203705</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I33" s="7">
-        <v>1428373</v>
+        <v>1423124</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O33" s="7"/>
     </row>
@@ -2309,38 +2318,38 @@
         <v>6</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" s="8">
-        <v>46027.4840625</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="E34" s="8">
-        <v>46027.4840625</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I34" s="7">
-        <v>1404289</v>
+        <v>1428373</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O34" s="7"/>
     </row>
@@ -2350,38 +2359,38 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D35" s="8">
-        <v>46030.397997685184</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="E35" s="8">
-        <v>46030.397997685184</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I35" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O35" s="7"/>
     </row>
@@ -2391,612 +2400,612 @@
         <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D36" s="8">
-        <v>46030.408148148148</v>
+        <v>46086.434641203705</v>
       </c>
       <c r="E36" s="8">
-        <v>46030.408148148148</v>
+        <v>46086.434641203705</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I36" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O36" s="7"/>
     </row>
     <row r="37" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D37" s="8">
-        <v>46030.478854166664</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E37" s="8">
-        <v>46030.478854166664</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I37" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O37" s="7"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D38" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E38" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I38" s="7">
         <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O38" s="7"/>
     </row>
     <row r="39" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E39" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I39" s="7">
         <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O39" s="7"/>
     </row>
     <row r="40" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D40" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E40" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I40" s="7">
         <v>1394724</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O40" s="7"/>
     </row>
     <row r="41" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D41" s="8">
-        <v>46043.565196759257</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E41" s="8">
-        <v>46043.565196759257</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I41" s="7">
         <v>1394724</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O41" s="7"/>
     </row>
     <row r="42" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D42" s="8">
-        <v>46069.559953703705</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E42" s="8">
-        <v>46069.559953703705</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I42" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O42" s="7"/>
     </row>
     <row r="43" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D43" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E43" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I43" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O43" s="7"/>
     </row>
     <row r="44" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D44" s="8">
-        <v>46080.522418981483</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E44" s="8">
-        <v>46080.522418981483</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I44" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>101</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O44" s="7"/>
     </row>
     <row r="45" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D45" s="8">
-        <v>46080.532164351855</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E45" s="8">
-        <v>46080.532164351855</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I45" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O45" s="7"/>
     </row>
     <row r="46" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D46" s="8">
-        <v>46083.531342592592</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="E46" s="8">
-        <v>46083.531342592592</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I46" s="7">
-        <v>1422283</v>
+        <v>1422286</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O46" s="7"/>
     </row>
     <row r="47" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D47" s="8">
-        <v>46085.365902777776</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="E47" s="8">
-        <v>46085.365902777776</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I47" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O47" s="7"/>
     </row>
     <row r="48" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D48" s="8">
-        <v>46086.317847222221</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="E48" s="8">
-        <v>46086.317847222221</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I48" s="7">
-        <v>1428242</v>
+        <v>1422285</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O48" s="7"/>
     </row>
     <row r="49" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D49" s="8">
-        <v>46087.292048611111</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="E49" s="8">
-        <v>46087.292048611111</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I49" s="7">
-        <v>1422282</v>
+        <v>1422283</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O49" s="7"/>
     </row>
     <row r="50" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D50" s="8">
-        <v>46087.575972222221</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="E50" s="8">
-        <v>46087.575972222221</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I50" s="7">
-        <v>1422282</v>
+        <v>1422283</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O50" s="7"/>
     </row>
@@ -3006,34 +3015,34 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D51" s="8">
-        <v>46035.47824074074</v>
+        <v>46086.317847222221</v>
       </c>
       <c r="E51" s="8">
-        <v>46035.47824074074</v>
+        <v>46086.317847222221</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I51" s="7">
-        <v>1404958</v>
+        <v>1428242</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
@@ -3047,38 +3056,38 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D52" s="8">
-        <v>46043.385196759256</v>
+        <v>46087.292048611111</v>
       </c>
       <c r="E52" s="8">
-        <v>46043.385196759256</v>
+        <v>46087.292048611111</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I52" s="7">
-        <v>1405794</v>
+        <v>1422282</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -3088,75 +3097,75 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D53" s="8">
-        <v>46043.385289351849</v>
+        <v>46087.575972222221</v>
       </c>
       <c r="E53" s="8">
-        <v>46043.385289351849</v>
+        <v>46087.575972222221</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I53" s="7">
-        <v>1405794</v>
+        <v>1422282</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O53" s="7"/>
     </row>
     <row r="54" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D54" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E54" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I54" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
@@ -3167,365 +3176,365 @@
     <row r="55" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D55" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E55" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I55" s="7">
         <v>1405794</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O55" s="7"/>
     </row>
     <row r="56" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D56" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E56" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I56" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O56" s="7"/>
     </row>
     <row r="57" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D57" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E57" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I57" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O57" s="7"/>
     </row>
     <row r="58" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D58" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E58" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I58" s="7">
-        <v>1410338</v>
+        <v>1405794</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O58" s="7"/>
     </row>
     <row r="59" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D59" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E59" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I59" s="7">
-        <v>1412987</v>
+        <v>1411351</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O59" s="7"/>
     </row>
     <row r="60" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D60" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E60" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I60" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O60" s="7"/>
     </row>
     <row r="61" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D61" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E61" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I61" s="7">
-        <v>1421099</v>
+        <v>1410338</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O61" s="7"/>
     </row>
     <row r="62" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D62" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E62" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I62" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O62" s="7"/>
     </row>
     <row r="63" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D63" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E63" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I63" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
@@ -3536,251 +3545,251 @@
     <row r="64" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D64" s="8">
-        <v>46085.366041666668</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E64" s="8">
-        <v>46085.366041666668</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I64" s="7">
-        <v>1423125</v>
+        <v>1421099</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O64" s="7"/>
     </row>
     <row r="65" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D65" s="8">
-        <v>46090.39471064815</v>
+        <v>46077.368379629632</v>
       </c>
       <c r="E65" s="8">
-        <v>46090.39471064815</v>
+        <v>46077.368379629632</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I65" s="7">
-        <v>1410769</v>
+        <v>1422285</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O65" s="7"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A66" s="4"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="9">
-        <v>0</v>
-      </c>
-      <c r="N66" s="9">
-        <v>261</v>
-      </c>
-      <c r="O66" s="9">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B67" s="12" t="s">
+    <row r="66" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A66" s="2"/>
+      <c r="B66" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12"/>
-      <c r="O67" s="12"/>
+      <c r="C66" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E66" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I66" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10">
+        <v>3</v>
+      </c>
+      <c r="O66" s="7"/>
+    </row>
+    <row r="67" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A67" s="2"/>
+      <c r="B67" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" s="8">
+        <v>46085.366041666668</v>
+      </c>
+      <c r="E67" s="8">
+        <v>46085.366041666668</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I67" s="7">
+        <v>1423125</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10">
+        <v>5</v>
+      </c>
+      <c r="O67" s="7"/>
     </row>
     <row r="68" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D68" s="8">
-        <v>46027.666331018518</v>
+        <v>46090.39471064815</v>
       </c>
       <c r="E68" s="8">
-        <v>46027.666331018518</v>
+        <v>46090.39471064815</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I68" s="7">
-        <v>1386388</v>
+        <v>1410769</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7"/>
     </row>
-    <row r="69" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A69" s="2"/>
-      <c r="B69" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D69" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E69" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I69" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K69" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10">
-        <v>1</v>
-      </c>
-      <c r="O69" s="7"/>
-    </row>
-    <row r="70" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A70" s="2"/>
-      <c r="B70" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D70" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="E70" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I70" s="7">
-        <v>1406206</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="K70" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="L70" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10">
-        <v>11</v>
-      </c>
-      <c r="O70" s="7"/>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A69" s="4"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="9">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9">
+        <v>274</v>
+      </c>
+      <c r="O69" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
     </row>
     <row r="71" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
@@ -3788,38 +3797,38 @@
         <v>4</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D71" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E71" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I71" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>86</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3829,38 +3838,38 @@
         <v>4</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D72" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E72" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I72" s="7">
-        <v>1411990</v>
+        <v>1386388</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3873,35 +3882,35 @@
         <v>41</v>
       </c>
       <c r="D73" s="8">
-        <v>46065.655185185184</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E73" s="8">
-        <v>46065.655185185184</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I73" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3914,35 +3923,35 @@
         <v>42</v>
       </c>
       <c r="D74" s="8">
-        <v>46066.613657407404</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E74" s="8">
-        <v>46066.613657407404</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I74" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3952,34 +3961,34 @@
         <v>4</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D75" s="8">
-        <v>46066.670127314814</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E75" s="8">
-        <v>46066.670127314814</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I75" s="7">
         <v>1411990</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
@@ -3996,35 +4005,35 @@
         <v>43</v>
       </c>
       <c r="D76" s="8">
-        <v>46079.703912037039</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E76" s="8">
-        <v>46079.703912037039</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I76" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -4037,35 +4046,35 @@
         <v>44</v>
       </c>
       <c r="D77" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E77" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I77" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4078,35 +4087,35 @@
         <v>44</v>
       </c>
       <c r="D78" s="8">
-        <v>46084.883263888885</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E78" s="8">
-        <v>46084.883263888885</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I78" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4119,35 +4128,35 @@
         <v>45</v>
       </c>
       <c r="D79" s="8">
-        <v>46091.687349537038</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E79" s="8">
-        <v>46091.687349537038</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I79" s="7">
-        <v>1423607</v>
+        <v>1410767</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4157,38 +4166,38 @@
         <v>4</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D80" s="8">
-        <v>46091.708692129629</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E80" s="8">
-        <v>46091.708692129629</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I80" s="7">
-        <v>1423607</v>
+        <v>1428327</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O80" s="7"/>
     </row>
@@ -4198,34 +4207,34 @@
         <v>4</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D81" s="8">
-        <v>46091.738194444442</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E81" s="8">
-        <v>46091.738194444442</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I81" s="7">
-        <v>1423607</v>
+        <v>1428327</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
@@ -4236,78 +4245,78 @@
     <row r="82" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D82" s="8">
-        <v>46088.746967592589</v>
+        <v>46091.687349537038</v>
       </c>
       <c r="E82" s="8">
-        <v>46088.746967592589</v>
+        <v>46091.687349537038</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I82" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O82" s="7"/>
     </row>
     <row r="83" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D83" s="8">
-        <v>46088.837569444448</v>
+        <v>46091.708692129629</v>
       </c>
       <c r="E83" s="8">
-        <v>46088.837569444448</v>
+        <v>46091.708692129629</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I83" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
@@ -4318,37 +4327,37 @@
     <row r="84" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D84" s="8">
-        <v>46088.841886574075</v>
+        <v>46091.738194444442</v>
       </c>
       <c r="E84" s="8">
-        <v>46088.841886574075</v>
+        <v>46091.738194444442</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I84" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
@@ -4359,107 +4368,107 @@
     <row r="85" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D85" s="8">
-        <v>46088.849849537037</v>
+        <v>46093.693726851852</v>
       </c>
       <c r="E85" s="8">
-        <v>46088.849849537037</v>
+        <v>46093.693726851852</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I85" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O85" s="7"/>
     </row>
     <row r="86" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D86" s="8">
-        <v>46090.828055555554</v>
+        <v>46093.714236111111</v>
       </c>
       <c r="E86" s="8">
-        <v>46090.828055555554</v>
+        <v>46093.714236111111</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I86" s="7">
-        <v>1427431</v>
+        <v>1423607</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O86" s="7"/>
     </row>
     <row r="87" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D87" s="8">
-        <v>46091.686921296299</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="E87" s="8">
-        <v>46091.686921296299</v>
+        <v>46088.746967592589</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I87" s="7">
         <v>1427431</v>
@@ -4468,39 +4477,39 @@
         <v>92</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O87" s="7"/>
     </row>
     <row r="88" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D88" s="8">
-        <v>46091.72351851852</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="E88" s="8">
-        <v>46091.72351851852</v>
+        <v>46088.837569444448</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I88" s="7">
         <v>1427431</v>
@@ -4509,39 +4518,39 @@
         <v>92</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O88" s="7"/>
     </row>
     <row r="89" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D89" s="8">
-        <v>46091.737939814811</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="E89" s="8">
-        <v>46091.737939814811</v>
+        <v>46088.841886574075</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I89" s="7">
         <v>1427431</v>
@@ -4550,10 +4559,10 @@
         <v>92</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
@@ -4564,25 +4573,25 @@
     <row r="90" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D90" s="8">
-        <v>46091.838368055556</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="E90" s="8">
-        <v>46091.838368055556</v>
+        <v>46088.849849537037</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I90" s="7">
         <v>1427431</v>
@@ -4591,14 +4600,14 @@
         <v>92</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O90" s="7"/>
     </row>
@@ -4608,38 +4617,38 @@
         <v>5</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D91" s="8">
-        <v>46028.907905092594</v>
+        <v>46090.828055555554</v>
       </c>
       <c r="E91" s="8">
-        <v>46028.907905092594</v>
+        <v>46090.828055555554</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I91" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O91" s="7"/>
     </row>
@@ -4652,35 +4661,35 @@
         <v>47</v>
       </c>
       <c r="D92" s="8">
-        <v>46029.6719212963</v>
+        <v>46091.686921296299</v>
       </c>
       <c r="E92" s="8">
-        <v>46029.6719212963</v>
+        <v>46091.686921296299</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I92" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O92" s="7"/>
     </row>
@@ -4690,38 +4699,38 @@
         <v>5</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D93" s="8">
-        <v>46034.72855324074</v>
+        <v>46091.72351851852</v>
       </c>
       <c r="E93" s="8">
-        <v>46034.72855324074</v>
+        <v>46091.72351851852</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I93" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O93" s="7"/>
     </row>
@@ -4731,38 +4740,38 @@
         <v>5</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D94" s="8">
-        <v>46037.838958333334</v>
+        <v>46091.737939814811</v>
       </c>
       <c r="E94" s="8">
-        <v>46037.838958333334</v>
+        <v>46091.737939814811</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I94" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O94" s="7"/>
     </row>
@@ -4772,38 +4781,38 @@
         <v>5</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D95" s="8">
-        <v>46042.727754629632</v>
+        <v>46091.838368055556</v>
       </c>
       <c r="E95" s="8">
-        <v>46042.727754629632</v>
+        <v>46091.838368055556</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I95" s="7">
-        <v>1394721</v>
+        <v>1427431</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4813,38 +4822,38 @@
         <v>5</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D96" s="8">
-        <v>46043.627881944441</v>
+        <v>46093.687141203707</v>
       </c>
       <c r="E96" s="8">
-        <v>46043.627881944441</v>
+        <v>46093.687141203707</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I96" s="7">
-        <v>1410339</v>
+        <v>1433590</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O96" s="7"/>
     </row>
@@ -4854,321 +4863,321 @@
         <v>5</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="D97" s="8">
-        <v>46052.626018518517</v>
+        <v>46093.729467592595</v>
       </c>
       <c r="E97" s="8">
-        <v>46052.626018518517</v>
+        <v>46093.729467592595</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I97" s="7">
-        <v>1411706</v>
+        <v>1433590</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L97" s="7" t="s">
         <v>124</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O97" s="7"/>
     </row>
     <row r="98" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D98" s="8">
-        <v>46053.632291666669</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E98" s="8">
-        <v>46053.632291666669</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I98" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L98" s="7" t="s">
         <v>124</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O98" s="7"/>
     </row>
     <row r="99" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D99" s="8">
-        <v>46071.601446759261</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E99" s="8">
-        <v>46071.601446759261</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I99" s="7">
-        <v>1418251</v>
+        <v>1394721</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O99" s="7"/>
     </row>
     <row r="100" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D100" s="8">
-        <v>46076.679282407407</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E100" s="8">
-        <v>46076.679282407407</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I100" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>94</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O100" s="7"/>
     </row>
     <row r="101" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D101" s="8">
-        <v>46077.591944444444</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E101" s="8">
-        <v>46077.591944444444</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>72</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I101" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>94</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O101" s="7"/>
     </row>
     <row r="102" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="D102" s="8">
-        <v>46077.861296296294</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E102" s="8">
-        <v>46077.861296296294</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I102" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>94</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O102" s="7"/>
     </row>
     <row r="103" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D103" s="8">
-        <v>46086.860844907409</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E103" s="8">
-        <v>46086.860844907409</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I103" s="7">
-        <v>1428373</v>
+        <v>1410339</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O103" s="7"/>
     </row>
     <row r="104" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D104" s="8">
-        <v>46091.867337962962</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E104" s="8">
-        <v>46091.867337962962</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I104" s="7">
-        <v>1428373</v>
+        <v>1411706</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M104" s="10"/>
       <c r="N104" s="10">
@@ -5182,38 +5191,38 @@
         <v>6</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D105" s="8">
-        <v>46027.633611111109</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E105" s="8">
-        <v>46027.633611111109</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I105" s="7">
-        <v>1404289</v>
+        <v>1411708</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M105" s="10"/>
       <c r="N105" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O105" s="7"/>
     </row>
@@ -5223,38 +5232,38 @@
         <v>6</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D106" s="8">
-        <v>46029.802372685182</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E106" s="8">
-        <v>46029.802372685182</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>74</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I106" s="7">
-        <v>1394724</v>
+        <v>1418251</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="K106" s="5" t="s">
         <v>119</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M106" s="10"/>
       <c r="N106" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O106" s="7"/>
     </row>
@@ -5264,38 +5273,38 @@
         <v>6</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="D107" s="8">
-        <v>46030.908472222225</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E107" s="8">
-        <v>46030.908472222225</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I107" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K107" s="5" t="s">
         <v>119</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O107" s="7"/>
     </row>
@@ -5305,34 +5314,34 @@
         <v>6</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D108" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E108" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I108" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K108" s="5" t="s">
         <v>119</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M108" s="10"/>
       <c r="N108" s="10">
@@ -5346,38 +5355,38 @@
         <v>6</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D109" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E109" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I109" s="7">
-        <v>1422286</v>
+        <v>1422511</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K109" s="5" t="s">
         <v>119</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M109" s="10"/>
       <c r="N109" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O109" s="7"/>
     </row>
@@ -5387,38 +5396,38 @@
         <v>6</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D110" s="8">
-        <v>46078.867326388892</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="E110" s="8">
-        <v>46078.867326388892</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I110" s="7">
-        <v>1422286</v>
+        <v>1428373</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M110" s="10"/>
       <c r="N110" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O110" s="7"/>
     </row>
@@ -5428,34 +5437,34 @@
         <v>6</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D111" s="8">
-        <v>46080.639293981483</v>
+        <v>46091.867337962962</v>
       </c>
       <c r="E111" s="8">
-        <v>46080.639293981483</v>
+        <v>46091.867337962962</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I111" s="7">
-        <v>1422285</v>
+        <v>1428373</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M111" s="10"/>
       <c r="N111" s="10">
@@ -5466,365 +5475,365 @@
     <row r="112" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D112" s="8">
-        <v>46080.716932870368</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E112" s="8">
-        <v>46080.716932870368</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I112" s="7">
-        <v>1422285</v>
+        <v>1404289</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M112" s="10"/>
       <c r="N112" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O112" s="7"/>
     </row>
     <row r="113" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D113" s="8">
-        <v>46080.740543981483</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E113" s="8">
-        <v>46080.740543981483</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I113" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J113" s="5" t="s">
         <v>101</v>
       </c>
       <c r="K113" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M113" s="10"/>
       <c r="N113" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O113" s="7"/>
     </row>
     <row r="114" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="D114" s="8">
-        <v>46081.588483796295</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E114" s="8">
-        <v>46081.588483796295</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I114" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>101</v>
       </c>
       <c r="K114" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M114" s="10"/>
       <c r="N114" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O114" s="7"/>
     </row>
     <row r="115" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D115" s="8">
-        <v>46083.87841435185</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E115" s="8">
-        <v>46083.87841435185</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I115" s="7">
-        <v>1422283</v>
+        <v>1394724</v>
       </c>
       <c r="J115" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K115" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M115" s="10"/>
       <c r="N115" s="10">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="O115" s="7"/>
     </row>
     <row r="116" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D116" s="8">
-        <v>46087.689409722225</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E116" s="8">
-        <v>46087.689409722225</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I116" s="7">
-        <v>1422282</v>
+        <v>1422286</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="K116" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O116" s="7"/>
     </row>
     <row r="117" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D117" s="8">
-        <v>46088.641435185185</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E117" s="8">
-        <v>46088.641435185185</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I117" s="7">
-        <v>1422282</v>
+        <v>1422286</v>
       </c>
       <c r="J117" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="K117" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="M117" s="10"/>
       <c r="N117" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O117" s="7"/>
     </row>
     <row r="118" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D118" s="8">
-        <v>46088.69903935185</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E118" s="8">
-        <v>46088.69903935185</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I118" s="7">
-        <v>1422282</v>
+        <v>1422285</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O118" s="7"/>
     </row>
     <row r="119" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D119" s="8">
-        <v>46090.906782407408</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E119" s="8">
-        <v>46090.906782407408</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I119" s="7">
-        <v>1428249</v>
+        <v>1422285</v>
       </c>
       <c r="J119" s="5" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="K119" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="M119" s="10"/>
       <c r="N119" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O119" s="7"/>
     </row>
     <row r="120" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D120" s="8">
-        <v>46090.910081018519</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E120" s="8">
-        <v>46090.910081018519</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I120" s="7">
-        <v>1428249</v>
+        <v>1422285</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="M120" s="10"/>
       <c r="N120" s="10">
@@ -5838,38 +5847,38 @@
         <v>7</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D121" s="8">
-        <v>46024.795127314814</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E121" s="8">
-        <v>46024.795127314814</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>74</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I121" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K121" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="M121" s="10"/>
       <c r="N121" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O121" s="7"/>
     </row>
@@ -5879,38 +5888,38 @@
         <v>7</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D122" s="8">
-        <v>46024.795277777775</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E122" s="8">
-        <v>46024.795277777775</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I122" s="7">
-        <v>1398335</v>
+        <v>1422283</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M122" s="10"/>
       <c r="N122" s="10">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O122" s="7"/>
     </row>
@@ -5920,38 +5929,38 @@
         <v>7</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D123" s="8">
-        <v>46024.900324074071</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="E123" s="8">
-        <v>46024.900324074071</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I123" s="7">
-        <v>1398335</v>
+        <v>1422282</v>
       </c>
       <c r="J123" s="5" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="K123" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L123" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M123" s="10"/>
       <c r="N123" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O123" s="7"/>
     </row>
@@ -5961,38 +5970,38 @@
         <v>7</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D124" s="8">
-        <v>46028.866898148146</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="E124" s="8">
-        <v>46028.866898148146</v>
+        <v>46088.641435185185</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I124" s="7">
-        <v>1402956</v>
+        <v>1422282</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K124" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M124" s="10"/>
       <c r="N124" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O124" s="7"/>
     </row>
@@ -6005,35 +6014,35 @@
         <v>48</v>
       </c>
       <c r="D125" s="8">
-        <v>46034.751261574071</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="E125" s="8">
-        <v>46034.751261574071</v>
+        <v>46088.69903935185</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I125" s="7">
-        <v>1404958</v>
+        <v>1422282</v>
       </c>
       <c r="J125" s="5" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="K125" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L125" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M125" s="10"/>
       <c r="N125" s="10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O125" s="7"/>
     </row>
@@ -6043,38 +6052,38 @@
         <v>7</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D126" s="8">
-        <v>46062.904895833337</v>
+        <v>46090.906782407408</v>
       </c>
       <c r="E126" s="8">
-        <v>46062.904895833337</v>
+        <v>46090.906782407408</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I126" s="7">
-        <v>1412987</v>
+        <v>1428249</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>88</v>
       </c>
       <c r="K126" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L126" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M126" s="10"/>
       <c r="N126" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O126" s="7"/>
     </row>
@@ -6084,333 +6093,620 @@
         <v>7</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D127" s="8">
-        <v>46063.874467592592</v>
+        <v>46090.910081018519</v>
       </c>
       <c r="E127" s="8">
-        <v>46063.874467592592</v>
+        <v>46090.910081018519</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I127" s="7">
-        <v>1412987</v>
+        <v>1428249</v>
       </c>
       <c r="J127" s="5" t="s">
         <v>88</v>
       </c>
       <c r="K127" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L127" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M127" s="10"/>
       <c r="N127" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O127" s="7"/>
     </row>
     <row r="128" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D128" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E128" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I128" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J128" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K128" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L128" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M128" s="10"/>
       <c r="N128" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O128" s="7"/>
     </row>
     <row r="129" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D129" s="8">
-        <v>46069.700543981482</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E129" s="8">
-        <v>46069.700543981482</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I129" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J129" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K129" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L129" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M129" s="10"/>
       <c r="N129" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O129" s="7"/>
     </row>
     <row r="130" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="D130" s="8">
-        <v>46077.65824074074</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E130" s="8">
-        <v>46077.65824074074</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I130" s="7">
-        <v>1422285</v>
+        <v>1398335</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="K130" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L130" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M130" s="10"/>
       <c r="N130" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O130" s="7"/>
     </row>
     <row r="131" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D131" s="8">
-        <v>46078.881018518521</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E131" s="8">
-        <v>46078.881018518521</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I131" s="7">
-        <v>1423123</v>
+        <v>1402956</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K131" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L131" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M131" s="10"/>
       <c r="N131" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O131" s="7"/>
     </row>
     <row r="132" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D132" s="8">
-        <v>46079.901782407411</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E132" s="8">
-        <v>46079.901782407411</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I132" s="7">
-        <v>1423123</v>
+        <v>1404958</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="K132" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L132" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M132" s="10"/>
       <c r="N132" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O132" s="7"/>
     </row>
     <row r="133" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D133" s="8">
-        <v>46090.910266203704</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E133" s="8">
-        <v>46090.910266203704</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G133" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I133" s="7">
-        <v>1410772</v>
+        <v>1412987</v>
       </c>
       <c r="J133" s="5" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="K133" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L133" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M133" s="10"/>
       <c r="N133" s="10">
+        <v>1</v>
+      </c>
+      <c r="O133" s="7"/>
+    </row>
+    <row r="134" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A134" s="2"/>
+      <c r="B134" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D134" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="E134" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H134" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I134" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J134" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K134" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L134" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M134" s="10"/>
+      <c r="N134" s="10">
+        <v>5</v>
+      </c>
+      <c r="O134" s="7"/>
+    </row>
+    <row r="135" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A135" s="2"/>
+      <c r="B135" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D135" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E135" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I135" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J135" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="K135" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L135" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="M135" s="10"/>
+      <c r="N135" s="10">
         <v>3</v>
       </c>
-      <c r="O133" s="7"/>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A134" s="4"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
-      <c r="M134" s="9">
+      <c r="O135" s="7"/>
+    </row>
+    <row r="136" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A136" s="2"/>
+      <c r="B136" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D136" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E136" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I136" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J136" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="K136" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L136" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="M136" s="10"/>
+      <c r="N136" s="10">
+        <v>10</v>
+      </c>
+      <c r="O136" s="7"/>
+    </row>
+    <row r="137" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A137" s="2"/>
+      <c r="B137" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D137" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E137" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H137" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I137" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J137" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K137" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L137" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="M137" s="10"/>
+      <c r="N137" s="10">
+        <v>1</v>
+      </c>
+      <c r="O137" s="7"/>
+    </row>
+    <row r="138" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A138" s="2"/>
+      <c r="B138" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D138" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E138" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I138" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J138" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K138" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L138" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M138" s="10"/>
+      <c r="N138" s="10">
+        <v>1</v>
+      </c>
+      <c r="O138" s="7"/>
+    </row>
+    <row r="139" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A139" s="2"/>
+      <c r="B139" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D139" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E139" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I139" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J139" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K139" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L139" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M139" s="10"/>
+      <c r="N139" s="10">
+        <v>1</v>
+      </c>
+      <c r="O139" s="7"/>
+    </row>
+    <row r="140" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A140" s="2"/>
+      <c r="B140" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D140" s="8">
+        <v>46090.910266203704</v>
+      </c>
+      <c r="E140" s="8">
+        <v>46090.910266203704</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I140" s="7">
+        <v>1410772</v>
+      </c>
+      <c r="J140" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="K140" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L140" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M140" s="10"/>
+      <c r="N140" s="10">
+        <v>3</v>
+      </c>
+      <c r="O140" s="7"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A141" s="4"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="6"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="6"/>
+      <c r="J141" s="6"/>
+      <c r="K141" s="6"/>
+      <c r="L141" s="6"/>
+      <c r="M141" s="9">
         <v>0</v>
       </c>
-      <c r="N134" s="9">
-        <v>315</v>
-      </c>
-      <c r="O134" s="9">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A135" s="4"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="9">
-        <v>128</v>
-      </c>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
-      <c r="M135" s="9">
+      <c r="N141" s="9">
+        <v>337</v>
+      </c>
+      <c r="O141" s="9">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A142" s="4"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="6"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6"/>
+      <c r="H142" s="9">
+        <v>135</v>
+      </c>
+      <c r="I142" s="6"/>
+      <c r="J142" s="6"/>
+      <c r="K142" s="6"/>
+      <c r="L142" s="6"/>
+      <c r="M142" s="9">
         <v>0</v>
       </c>
-      <c r="N135" s="9">
-        <v>576</v>
-      </c>
-      <c r="O135" s="9">
-        <v>128</v>
+      <c r="N142" s="9">
+        <v>611</v>
+      </c>
+      <c r="O142" s="9">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -6420,7 +6716,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B67:O67"/>
+    <mergeCell ref="B70:O70"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6DFE4AE-9797-4347-9E50-26601CF1040B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10E71E57-8314-4230-9CB1-CDC84E649159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{91E89078-AA4C-474D-B912-6FF611353892}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{089D0EF2-2B28-4237-98C7-43B0F519A118}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -972,7 +972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3AA45F3-C7AE-4783-97EB-8C6A289F7541}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3F16FD-8BD2-4DD8-9334-60B5DB251526}">
   <dimension ref="A1:O142"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
